--- a/JsonConverter/ExcelFiles/CBAEvent.xlsx
+++ b/JsonConverter/ExcelFiles/CBAEvent.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\CBA\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF25D7B6-880C-4C50-AF92-37003396AEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE866F85-724A-4364-B71C-A6A786B9082F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1650" yWindow="2205" windowWidth="24660" windowHeight="12435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1530" yWindow="2160" windowWidth="26910" windowHeight="12435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CBAEvent" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
   <si>
     <t>string</t>
   </si>
@@ -36,299 +36,139 @@
     <t>Id</t>
   </si>
   <si>
-    <t>string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Event ID</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>이벤트 제목</t>
   </si>
   <si>
     <t>화면에 출력될 상황 설명</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BackgroundImagePath</t>
+  </si>
+  <si>
+    <t>NPCPrefabPath</t>
+  </si>
+  <si>
+    <t>선택지1</t>
+  </si>
+  <si>
+    <t>선택지2</t>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>걷다가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>돌뿌리를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>발견했다. 어엉..?</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>EventTitle</t>
+  </si>
+  <si>
+    <t>EventDescription</t>
+  </si>
+  <si>
+    <t>Choice1Text</t>
+  </si>
+  <si>
+    <t>Choice1SuccessResult</t>
+  </si>
+  <si>
+    <t>Choice1FailResult</t>
+  </si>
+  <si>
+    <t>Choice1SuccessProbability</t>
+  </si>
+  <si>
+    <t>Choice2Text</t>
+  </si>
+  <si>
+    <t>Choice2SuccessResult</t>
+  </si>
+  <si>
+    <t>Choice2FailResult</t>
+  </si>
+  <si>
+    <t>Choice2SuccessProbability</t>
+  </si>
+  <si>
+    <t>event_1</t>
+  </si>
+  <si>
+    <t>돌뿌리 발견</t>
+  </si>
+  <si>
+    <t>걷다가 돌뿌리를 발견했다. 어엉..?</t>
   </si>
   <si>
     <t>점프해서 넘어가볼까?</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>점프에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>성공했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">! </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>촤핫!</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>점프에 성공했다! 촤핫!</t>
+  </si>
+  <si>
+    <t>넘어졌다! 무릎이 까졌어..</t>
+  </si>
+  <si>
+    <t>돌아서 안전하게 가자.</t>
   </si>
   <si>
     <t>안전하게 돌아갔다! 안전제일이지!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌아가다 길을 잃었다..</t>
+  </si>
+  <si>
+    <t>event_2</t>
+  </si>
+  <si>
+    <t>꿀단지 발견</t>
   </si>
   <si>
     <t>꿀단지를 발견했다. 침이 흐른다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>맛있게 먹는다. 냠!</t>
+  </si>
+  <si>
+    <t>기운이 솟는다!! 우어!!!</t>
+  </si>
+  <si>
+    <t>혈당 스파이크… zZZzzzZZ..</t>
   </si>
   <si>
     <t>의심스러워.. 먹지 않는다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>현명한 선택. 길에 있는 건 먹지 말랬어</t>
+  </si>
+  <si>
+    <t>참다 못해 결국 먹었다..</t>
   </si>
   <si>
     <t>event_3</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>이벤트 제목</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>EventTitle</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌뿌리 발견</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>꿀단지 발견</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>나무 발견</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>EventDescription</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>BackgroundImagePath</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPCPrefabPath</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ChoiceText</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuccessResultText</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>넘어졌다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">! </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>무릎이 까졌어..</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>FailResultText</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>선택지1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>선택지2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌아서 안전하게 가자.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌아가다 길을 잃었다..</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>기운이 솟는다!! 우어!!!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>맛있게 먹는다. 냠!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>혈당 스파이크… zZZzzzZZ..</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>현명한 선택. 길에 있는 건 먹지 말랬어</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>참다 못해 결국 먹었다..</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">멋진 나무를 발견했다. </t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>말을 걸어보자.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>째려볼 뿐 아무 반응이 없다. 방해하지 말자…</t>
+  </si>
+  <si>
+    <t>나무에게 말 걸지 말라고 혼났다. 내향형인가보다…</t>
   </si>
   <si>
     <t>밑에서 낮잠을 잔다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무에게 말 걸지 말라고 혼났다. 내향형인가보다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>째려볼 뿐 아무 반응이 없다. 방해하지 말자…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>그늘이 시원해서 기분이 좋다. 헷~</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>나무가 저리 가라며 쫓아냈다… 너무해 엉엉</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuccessProbability</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -469,7 +309,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -508,19 +348,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -548,7 +375,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -614,22 +441,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -871,39 +688,39 @@
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F1" s="31" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="33"/>
       <c r="J1" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="36"/>
+        <v>8</v>
+      </c>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="33"/>
     </row>
     <row r="2" spans="1:15" ht="12.75">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>0</v>
@@ -912,31 +729,31 @@
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J2" s="25" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:15" s="12" customFormat="1" ht="15.75" customHeight="1">
@@ -944,59 +761,59 @@
         <v>1</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" s="26" t="s">
-        <v>23</v>
-      </c>
       <c r="K3" s="20" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="M3" s="20" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="21"/>
       <c r="F4" s="4" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>25</v>
@@ -1005,13 +822,13 @@
         <v>60</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K4" s="18" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M4" s="5">
         <v>80</v>
@@ -1021,34 +838,34 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>32</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I5" s="22">
         <v>50</v>
       </c>
       <c r="J5" s="23" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M5" s="5">
         <v>50</v>
@@ -1058,34 +875,34 @@
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I6" s="22">
         <v>20</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="M6" s="5">
         <v>80</v>

--- a/JsonConverter/ExcelFiles/CBAEvent.xlsx
+++ b/JsonConverter/ExcelFiles/CBAEvent.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\CBA\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE866F85-724A-4364-B71C-A6A786B9082F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D58B57CD-5E37-441C-AD55-3C1799638076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="2160" windowWidth="26910" windowHeight="12435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="375" yWindow="1845" windowWidth="26970" windowHeight="12435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CBAEvent" sheetId="1" r:id="rId1"/>
@@ -156,19 +156,20 @@
     <t>말을 걸어보자.</t>
   </si>
   <si>
+    <t>나무에게 말 걸지 말라고 혼났다. 내향형인가보다…</t>
+  </si>
+  <si>
+    <t>밑에서 낮잠을 잔다.</t>
+  </si>
+  <si>
+    <t>그늘이 시원해서 기분이 좋다. 헷~</t>
+  </si>
+  <si>
+    <t>나무가 저리 가라며 쫓아냈다… 너무해 엉엉</t>
+  </si>
+  <si>
     <t>째려볼 뿐 아무 반응이 없다. 방해하지 말자…</t>
-  </si>
-  <si>
-    <t>나무에게 말 걸지 말라고 혼났다. 내향형인가보다…</t>
-  </si>
-  <si>
-    <t>밑에서 낮잠을 잔다.</t>
-  </si>
-  <si>
-    <t>그늘이 시원해서 기분이 좋다. 헷~</t>
-  </si>
-  <si>
-    <t>나무가 저리 가라며 쫓아냈다… 너무해 엉엉</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -887,22 +888,22 @@
         <v>41</v>
       </c>
       <c r="G6" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="I6" s="22">
         <v>20</v>
       </c>
       <c r="J6" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="L6" s="23" t="s">
         <v>45</v>
-      </c>
-      <c r="L6" s="23" t="s">
-        <v>46</v>
       </c>
       <c r="M6" s="5">
         <v>80</v>

--- a/JsonConverter/ExcelFiles/CBAEvent.xlsx
+++ b/JsonConverter/ExcelFiles/CBAEvent.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\CBA\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D58B57CD-5E37-441C-AD55-3C1799638076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAE6493-6A2C-48D2-B9AE-8CD32C127743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="375" yWindow="1845" windowWidth="26970" windowHeight="12435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CBAEvent" sheetId="1" r:id="rId1"/>
@@ -96,24 +96,12 @@
     <t>돌뿌리 발견</t>
   </si>
   <si>
-    <t>걷다가 돌뿌리를 발견했다. 어엉..?</t>
-  </si>
-  <si>
     <t>점프해서 넘어가볼까?</t>
   </si>
   <si>
-    <t>점프에 성공했다! 촤핫!</t>
-  </si>
-  <si>
-    <t>넘어졌다! 무릎이 까졌어..</t>
-  </si>
-  <si>
     <t>돌아서 안전하게 가자.</t>
   </si>
   <si>
-    <t>안전하게 돌아갔다! 안전제일이지!</t>
-  </si>
-  <si>
     <t>돌아가다 길을 잃었다..</t>
   </si>
   <si>
@@ -123,52 +111,209 @@
     <t>꿀단지 발견</t>
   </si>
   <si>
-    <t>꿀단지를 발견했다. 침이 흐른다.</t>
-  </si>
-  <si>
     <t>맛있게 먹는다. 냠!</t>
   </si>
   <si>
+    <t>참다 못해 결국 먹었다..</t>
+  </si>
+  <si>
+    <t>event_3</t>
+  </si>
+  <si>
+    <t>나무 발견</t>
+  </si>
+  <si>
+    <t xml:space="preserve">멋진 나무를 발견했다. </t>
+  </si>
+  <si>
+    <t>말을 걸어보자.</t>
+  </si>
+  <si>
+    <t>밑에서 낮잠을 잔다.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>걷다가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>돌뿌리를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>발견했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어엉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>..?</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>꿀단지를 발견했다. \n침이 흐른다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>넘어졌다! \n무릎이 까졌어..</t>
+  </si>
+  <si>
+    <t>안전하게 돌아갔다! \n안전제일이지!</t>
+  </si>
+  <si>
+    <t>째려볼 뿐 아무 반응이 없다. \n방해하지 말자…</t>
+  </si>
+  <si>
+    <t>나무에게 말 걸지 말라고 혼났다. \n내향형인가보다…</t>
+  </si>
+  <si>
+    <t>그늘이 시원해서 기분이 좋다. \n헷~</t>
+  </si>
+  <si>
+    <t>의심스러워.. 먹지 않는다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>점프에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성공했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>촤핫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>!</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>기운이 솟는다!! 우어!!!</t>
-  </si>
-  <si>
-    <t>혈당 스파이크… zZZzzzZZ..</t>
-  </si>
-  <si>
-    <t>의심스러워.. 먹지 않는다.</t>
-  </si>
-  <si>
-    <t>현명한 선택. 길에 있는 건 먹지 말랬어</t>
-  </si>
-  <si>
-    <t>참다 못해 결국 먹었다..</t>
-  </si>
-  <si>
-    <t>event_3</t>
-  </si>
-  <si>
-    <t>나무 발견</t>
-  </si>
-  <si>
-    <t xml:space="preserve">멋진 나무를 발견했다. </t>
-  </si>
-  <si>
-    <t>말을 걸어보자.</t>
-  </si>
-  <si>
-    <t>나무에게 말 걸지 말라고 혼났다. 내향형인가보다…</t>
-  </si>
-  <si>
-    <t>밑에서 낮잠을 잔다.</t>
-  </si>
-  <si>
-    <t>그늘이 시원해서 기분이 좋다. 헷~</t>
-  </si>
-  <si>
-    <t>나무가 저리 가라며 쫓아냈다… 너무해 엉엉</t>
-  </si>
-  <si>
-    <t>째려볼 뿐 아무 반응이 없다. 방해하지 말자…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>혈당 스파이크… zZZzzzZZ..\n잠에 빠져든다..</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>현명한 선택. \n우리 엄마가 길에 있는 건 먹지 말랬어!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무가 저리 가라며 쫓아냈다… \n너무해 엉엉</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -806,30 +951,30 @@
         <v>21</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="21"/>
       <c r="F4" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="I4" s="21">
         <v>60</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K4" s="18" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M4" s="5">
         <v>80</v>
@@ -839,34 +984,34 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="I5" s="22">
         <v>50</v>
       </c>
       <c r="J5" s="23" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="M5" s="5">
         <v>50</v>
@@ -876,34 +1021,34 @@
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="H6" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="I6" s="22">
         <v>20</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M6" s="5">
         <v>80</v>

--- a/JsonConverter/ExcelFiles/CBAEvent.xlsx
+++ b/JsonConverter/ExcelFiles/CBAEvent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\CBA\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAE6493-6A2C-48D2-B9AE-8CD32C127743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85652FE4-E954-4A6F-8CF1-11845CF674E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="74">
   <si>
     <t>string</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>돌아서 안전하게 가자.</t>
-  </si>
-  <si>
-    <t>돌아가다 길을 잃었다..</t>
   </si>
   <si>
     <t>event_2</t>
@@ -309,11 +306,270 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>현명한 선택. \n우리 엄마가 길에 있는 건 먹지 말랬어!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>나무가 저리 가라며 쫓아냈다… \n너무해 엉엉</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌아가다 길을 잃었다.. \n나 길치다곰…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>현명한 선택이었다곰. \n우리 엄마가 길에 있는 건 먹지 말랬어!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>수상한 버섯</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>알록달록한 버섯을 발견했다.\n먹음직스럽기도 하고 수상하기도 하다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>일단 입에 댄다. 난 곰이니까!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>건강한 버섯이었다. 난 버섯을 좋아해! \n홍홍~</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>배가 꼬르륵 거리며 복통이 느껴진다…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>헉…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>뭘 먹은거지?ㅠㅠ</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 정도로 멍청하진 않다곰! 냄새만 맡는다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>냄새만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맡고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>현명하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지나쳤다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나를 뭐로 보는거야?</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>재채기가 멈추지 않는다...\n푸엑취!우엑취!!!\n훌쩍…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>길 잃은 아기새</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무 아래 아기새 한 마리가 떨어져 있다.\n가엾게 삐약삐약 울고 있다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>둥지에 올려준다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>아기새가 안전하게 둥지로 돌아갔다.\n기분이 따뜻해졌다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무에서 떨어졌다. 엉덩이가 아프다.\n아기새가 한심하게 쳐다본다ㅠㅠ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>마음은 무겁고 발걸음은 가볍다. (이거 맞지?)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>죄책감에 발이 무겁다…\n아기새야 미안해…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_6</t>
+  </si>
+  <si>
+    <t>돼지머리가 왜 여기에</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>입에 전재산 만 원을 물려주고 떠난다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무 일도 일어나지 않았다. 내 돈…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>길 한복판에 잘린 돼지머리를 발견했다.\n이게 뭐람?</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>발로 찬다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>돼지머리가 뻥 하고 날아가 사라졌다. 스트레스가 풀렸다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>빗나가서 발목을 삐었다… 힘만 썼다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>어미새가 근처에 있을거라 믿고 지나친다</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>갑자기 돼지머리가 말을 한다:\n이딴 코딱지를 누굴 줘?\n도로 가져가! 투테퉤!!</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -321,7 +577,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="16">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -395,6 +651,40 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="굴림"/>
       <family val="2"/>
       <charset val="129"/>
     </font>
@@ -521,7 +811,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -587,6 +877,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -817,7 +1115,7 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" style="3"/>
+    <col min="2" max="2" width="13.42578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="33.7109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="22.42578125" style="3" customWidth="1"/>
     <col min="5" max="5" width="14.140625" style="22" customWidth="1"/>
@@ -848,18 +1146,18 @@
       <c r="E1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="34" t="s">
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="33"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="37"/>
     </row>
     <row r="2" spans="1:15" ht="12.75">
       <c r="A2" s="1" t="s">
@@ -951,7 +1249,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="21"/>
@@ -959,10 +1257,10 @@
         <v>22</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I4" s="21">
         <v>60</v>
@@ -971,10 +1269,10 @@
         <v>23</v>
       </c>
       <c r="K4" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="M4" s="5">
         <v>80</v>
@@ -984,34 +1282,34 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="C5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>27</v>
-      </c>
       <c r="G5" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="I5" s="22">
         <v>50</v>
       </c>
       <c r="J5" s="23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M5" s="5">
         <v>50</v>
@@ -1021,34 +1319,34 @@
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F6" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="19" t="s">
-        <v>32</v>
-      </c>
       <c r="G6" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="I6" s="22">
         <v>20</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M6" s="5">
         <v>80</v>
@@ -1057,26 +1355,113 @@
       <c r="O6" s="5"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
+      <c r="A7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="22">
+        <v>50</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="5">
+        <v>60</v>
+      </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A8" s="4"/>
-      <c r="B8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
+      <c r="A8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="22">
+        <v>65</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="L8" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="M8" s="5">
+        <v>90</v>
+      </c>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
+      <c r="A9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="22">
+        <v>70</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="L9" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="M9" s="5">
+        <v>70</v>
+      </c>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
     </row>
@@ -1183,7 +1568,7 @@
     </row>
     <row r="16" spans="1:15" ht="15.75" customHeight="1">
       <c r="A16" s="4"/>
-      <c r="C16" s="16"/>
+      <c r="C16" s="31"/>
       <c r="D16" s="6"/>
       <c r="E16" s="21"/>
       <c r="F16" s="21"/>
@@ -1195,7 +1580,7 @@
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1">
       <c r="A17" s="4"/>
-      <c r="C17" s="16"/>
+      <c r="C17" s="31"/>
       <c r="D17" s="6"/>
       <c r="E17" s="21"/>
       <c r="F17" s="21"/>

--- a/JsonConverter/ExcelFiles/CBAEvent.xlsx
+++ b/JsonConverter/ExcelFiles/CBAEvent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\CBA\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85652FE4-E954-4A6F-8CF1-11845CF674E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FF3468-C7DB-43B7-BCDC-4152996FBAB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -334,10 +334,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>건강한 버섯이었다. 난 버섯을 좋아해! \n홍홍~</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -545,10 +541,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>아무 일도 일어나지 않았다. 내 돈…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>길 한복판에 잘린 돼지머리를 발견했다.\n이게 뭐람?</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -570,6 +562,14 @@
   </si>
   <si>
     <t>갑자기 돼지머리가 말을 한다:\n이딴 코딱지를 누굴 줘?\n도로 가져가! 투테퉤!!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>건강한 버섯이었다.\n난 버섯을 좋아해! 홍홍~</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무 일도 일어나지 않았다.\n내 돈…</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1368,22 +1368,22 @@
         <v>50</v>
       </c>
       <c r="G7" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="I7" s="22">
         <v>50</v>
       </c>
       <c r="J7" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="K7" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="K7" s="33" t="s">
+      <c r="L7" s="34" t="s">
         <v>54</v>
-      </c>
-      <c r="L7" s="34" t="s">
-        <v>55</v>
       </c>
       <c r="M7" s="5">
         <v>60</v>
@@ -1393,34 +1393,34 @@
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="C8" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="F8" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="G8" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="H8" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="I8" s="22">
         <v>65</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K8" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="L8" s="23" t="s">
         <v>62</v>
-      </c>
-      <c r="L8" s="23" t="s">
-        <v>63</v>
       </c>
       <c r="M8" s="5">
         <v>90</v>
@@ -1430,34 +1430,34 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="C9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>66</v>
-      </c>
       <c r="G9" s="19" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I9" s="22">
         <v>70</v>
       </c>
       <c r="J9" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9" s="23" t="s">
         <v>69</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="L9" s="23" t="s">
-        <v>71</v>
       </c>
       <c r="M9" s="5">
         <v>70</v>

--- a/JsonConverter/ExcelFiles/CBAEvent.xlsx
+++ b/JsonConverter/ExcelFiles/CBAEvent.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\CBA\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FF3468-C7DB-43B7-BCDC-4152996FBAB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EEE439-FB59-4978-9AFB-A2095FC18660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="375" yWindow="1845" windowWidth="26970" windowHeight="12435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CBAEvent" sheetId="1" r:id="rId1"/>
@@ -1275,7 +1275,7 @@
         <v>45</v>
       </c>
       <c r="M4" s="5">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
@@ -1300,7 +1300,7 @@
         <v>43</v>
       </c>
       <c r="I5" s="22">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J5" s="23" t="s">
         <v>40</v>
@@ -1312,7 +1312,7 @@
         <v>27</v>
       </c>
       <c r="M5" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
@@ -1337,7 +1337,7 @@
         <v>38</v>
       </c>
       <c r="I6" s="22">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J6" s="19" t="s">
         <v>32</v>
@@ -1349,7 +1349,7 @@
         <v>44</v>
       </c>
       <c r="M6" s="5">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
@@ -1386,7 +1386,7 @@
         <v>54</v>
       </c>
       <c r="M7" s="5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
@@ -1411,7 +1411,7 @@
         <v>60</v>
       </c>
       <c r="I8" s="22">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J8" s="19" t="s">
         <v>70</v>
@@ -1423,7 +1423,7 @@
         <v>62</v>
       </c>
       <c r="M8" s="5">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
@@ -1448,7 +1448,7 @@
         <v>71</v>
       </c>
       <c r="I9" s="22">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J9" s="19" t="s">
         <v>67</v>
@@ -1460,7 +1460,7 @@
         <v>69</v>
       </c>
       <c r="M9" s="5">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>

--- a/JsonConverter/ExcelFiles/CBAEvent.xlsx
+++ b/JsonConverter/ExcelFiles/CBAEvent.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\CBA\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EEE439-FB59-4978-9AFB-A2095FC18660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B31BAE5-F360-4E4E-943E-1F3883EA4B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="375" yWindow="1845" windowWidth="26970" windowHeight="12435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="2775" windowWidth="26970" windowHeight="12435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CBAEvent" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="76">
   <si>
     <t>string</t>
   </si>
@@ -571,6 +571,12 @@
   <si>
     <t>아무 일도 일어나지 않았다.\n내 돈…</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Backgrounds/NewBackground2048x1536</t>
+  </si>
+  <si>
+    <t>Backgrounds/Background</t>
   </si>
 </sst>
 </file>
@@ -811,7 +817,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -893,6 +899,7 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1117,7 +1124,7 @@
     <col min="1" max="1" width="9.7109375" style="3" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="33.7109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="22.42578125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" style="3" customWidth="1"/>
     <col min="5" max="5" width="14.140625" style="22" customWidth="1"/>
     <col min="6" max="6" width="21.42578125" style="22" customWidth="1"/>
     <col min="7" max="7" width="24.5703125" style="22" customWidth="1"/>
@@ -1251,7 +1258,9 @@
       <c r="C4" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="E4" s="21"/>
       <c r="F4" s="4" t="s">
         <v>22</v>
@@ -1290,6 +1299,9 @@
       <c r="C5" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="D5" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="F5" s="19" t="s">
         <v>26</v>
       </c>
@@ -1327,6 +1339,9 @@
       <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="D6" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="F6" s="19" t="s">
         <v>31</v>
       </c>
@@ -1364,6 +1379,9 @@
       <c r="C7" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="D7" s="39" t="s">
+        <v>75</v>
+      </c>
       <c r="F7" s="19" t="s">
         <v>50</v>
       </c>
@@ -1401,6 +1419,9 @@
       <c r="C8" s="18" t="s">
         <v>57</v>
       </c>
+      <c r="D8" s="39" t="s">
+        <v>75</v>
+      </c>
       <c r="F8" s="19" t="s">
         <v>58</v>
       </c>
@@ -1437,6 +1458,9 @@
       </c>
       <c r="C9" s="2" t="s">
         <v>66</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>75</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>65</v>

--- a/JsonConverter/ExcelFiles/CBAEvent.xlsx
+++ b/JsonConverter/ExcelFiles/CBAEvent.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\CBA\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B31BAE5-F360-4E4E-943E-1F3883EA4B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53F4734-8F18-4B14-AFF5-3A6191919717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="2775" windowWidth="26970" windowHeight="12435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="2130" windowWidth="26970" windowHeight="12435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CBAEvent" sheetId="1" r:id="rId1"/>
@@ -45,9 +45,6 @@
     <t>화면에 출력될 상황 설명</t>
   </si>
   <si>
-    <t>BackgroundImagePath</t>
-  </si>
-  <si>
     <t>NPCPrefabPath</t>
   </si>
   <si>
@@ -573,10 +570,15 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Backgrounds/NewBackground2048x1536</t>
-  </si>
-  <si>
-    <t>Backgrounds/Background</t>
+    <t>BackgroundImageKey</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Background</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>NewBackground2048x1536</t>
   </si>
 </sst>
 </file>
@@ -891,6 +893,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -899,7 +902,6 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1148,23 +1150,23 @@
         <v>4</v>
       </c>
       <c r="D1" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="F1" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="38"/>
     </row>
     <row r="2" spans="1:15" ht="12.75">
       <c r="A2" s="1" t="s">
@@ -1192,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>0</v>
@@ -1204,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:15" s="12" customFormat="1" ht="15.75" customHeight="1">
@@ -1212,76 +1214,76 @@
         <v>1</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="D3" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="28" t="s">
+      <c r="G3" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="H3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="I3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="J3" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="K3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="L3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="M3" s="20" t="s">
         <v>18</v>
-      </c>
-      <c r="M3" s="20" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>21</v>
-      </c>
       <c r="C4" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>74</v>
       </c>
       <c r="E4" s="21"/>
       <c r="F4" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I4" s="21">
         <v>60</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K4" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M4" s="5">
         <v>70</v>
@@ -1291,37 +1293,37 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="C5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>26</v>
-      </c>
       <c r="G5" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="I5" s="22">
         <v>55</v>
       </c>
       <c r="J5" s="23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M5" s="5">
         <v>45</v>
@@ -1331,37 +1333,37 @@
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="C6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>31</v>
-      </c>
       <c r="G6" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="I6" s="22">
         <v>40</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M6" s="5">
         <v>70</v>
@@ -1371,37 +1373,37 @@
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="C7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="19" t="s">
+      <c r="G7" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="I7" s="22">
         <v>50</v>
       </c>
       <c r="J7" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="33" t="s">
+      <c r="L7" s="34" t="s">
         <v>53</v>
-      </c>
-      <c r="L7" s="34" t="s">
-        <v>54</v>
       </c>
       <c r="M7" s="5">
         <v>55</v>
@@ -1411,37 +1413,37 @@
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="C8" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="D8" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="19" t="s">
+      <c r="G8" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="H8" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="I8" s="22">
         <v>60</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K8" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="L8" s="23" t="s">
         <v>61</v>
-      </c>
-      <c r="L8" s="23" t="s">
-        <v>62</v>
       </c>
       <c r="M8" s="5">
         <v>75</v>
@@ -1451,37 +1453,37 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="C9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>65</v>
-      </c>
       <c r="G9" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I9" s="22">
         <v>65</v>
       </c>
       <c r="J9" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="K9" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="K9" s="19" t="s">
+      <c r="L9" s="23" t="s">
         <v>68</v>
-      </c>
-      <c r="L9" s="23" t="s">
-        <v>69</v>
       </c>
       <c r="M9" s="5">
         <v>60</v>

--- a/JsonConverter/ExcelFiles/CBAEvent.xlsx
+++ b/JsonConverter/ExcelFiles/CBAEvent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\CBA\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53F4734-8F18-4B14-AFF5-3A6191919717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704A8338-082A-4AE6-9C72-20AB637191FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="735" yWindow="2130" windowWidth="26970" windowHeight="12435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="82">
   <si>
     <t>string</t>
   </si>
@@ -579,6 +579,29 @@
   </si>
   <si>
     <t>NewBackground2048x1536</t>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_BabyBird</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_HoneyPot</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Mushroom</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_PigHead</t>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Rock</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Tree</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -819,7 +842,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -901,6 +924,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1127,7 +1153,7 @@
     <col min="2" max="2" width="13.42578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="33.7109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="26.140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="22" customWidth="1"/>
+    <col min="5" max="5" width="31.42578125" style="22" customWidth="1"/>
     <col min="6" max="6" width="21.42578125" style="22" customWidth="1"/>
     <col min="7" max="7" width="24.5703125" style="22" customWidth="1"/>
     <col min="8" max="8" width="43.28515625" style="3" customWidth="1"/>
@@ -1263,7 +1289,9 @@
       <c r="D4" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E4" s="21"/>
+      <c r="E4" s="21" t="s">
+        <v>80</v>
+      </c>
       <c r="F4" s="4" t="s">
         <v>21</v>
       </c>
@@ -1304,6 +1332,9 @@
       <c r="D5" s="4" t="s">
         <v>74</v>
       </c>
+      <c r="E5" s="40" t="s">
+        <v>77</v>
+      </c>
       <c r="F5" s="19" t="s">
         <v>25</v>
       </c>
@@ -1344,6 +1375,9 @@
       <c r="D6" s="4" t="s">
         <v>74</v>
       </c>
+      <c r="E6" s="40" t="s">
+        <v>81</v>
+      </c>
       <c r="F6" s="19" t="s">
         <v>30</v>
       </c>
@@ -1384,6 +1418,9 @@
       <c r="D7" s="35" t="s">
         <v>75</v>
       </c>
+      <c r="E7" s="40" t="s">
+        <v>78</v>
+      </c>
       <c r="F7" s="19" t="s">
         <v>49</v>
       </c>
@@ -1424,6 +1461,9 @@
       <c r="D8" s="35" t="s">
         <v>75</v>
       </c>
+      <c r="E8" s="40" t="s">
+        <v>76</v>
+      </c>
       <c r="F8" s="19" t="s">
         <v>57</v>
       </c>
@@ -1463,6 +1503,9 @@
       </c>
       <c r="D9" s="35" t="s">
         <v>75</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>79</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>64</v>

--- a/JsonConverter/ExcelFiles/CBAEvent.xlsx
+++ b/JsonConverter/ExcelFiles/CBAEvent.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\CBA\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704A8338-082A-4AE6-9C72-20AB637191FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B6C9B2-E754-4A37-B1E3-437E4A5555F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="2130" windowWidth="26970" windowHeight="12435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CBAEvent" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="135">
   <si>
     <t>string</t>
   </si>
@@ -601,6 +601,362 @@
   </si>
   <si>
     <t>Prefabs/2D/NPC_CBA/NPC_Tree</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_7</t>
+  </si>
+  <si>
+    <t>스산한 무덤</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름도 없는 낡은 무덤을 발견했다.\n뭔가 묻혀있는 것 같기도 하고…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>파본다. 난 곰이니까!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>지나간다. 난 무서우니까!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>오래된 사과가 나왔다. 체력+1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>땅 파다 허리를 삐끗했다.. 크흡…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭔가 좋은 게 있었을까…? 아쉽다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_8</t>
+  </si>
+  <si>
+    <t>떨어진 감자</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>노릇하게 구워진 감자가 길 한복판에 떨어져 있다! 이게 웬 횡재냐!!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>먹는다. 난 곰이니까!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>누굴 거지로 아나? 안 먹는다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="굴림"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따끈한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="굴림"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감자를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="굴림"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>먹었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="굴림"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> +1</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오래 돼서 싹 난 감자였다…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>독이 올랐다…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>엉엉…</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>배가 고프지만 오늘도 양심을 지켰다...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>곰이 그런 게 어딨어?! 돌아가서 다시 먹어버렸다. 이거지!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_9</t>
+  </si>
+  <si>
+    <t>모래밭 도착</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>모래밭이 앞을 가로막는다.\n발이 빠질 것 같아…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌진한다. 난 쾌남이니까!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>천천히 조심히 건넌다. (흥…)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>오 모래가 생각보다 단단했다. 빠르게 통과했다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>시간이 걸렸지만 무사히 건넜다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>발이 빠져 허우적댔다… 나 쾌남 아니다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>발이 빠져서 지쳐버렸다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_10</t>
+  </si>
+  <si>
+    <t>빈 집…인가?</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>숲 한 가운데 집이 있다.\n안에서 맛있는 냄새가 난다(!)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>문을 두드린다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>창문으로 몰래 훔쳐본다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>친절한 할머니가 빵을 줬다. 히힛</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>갑자기 문이 열리며 무서운 개가 뛰어나왔다!!!!!! 꺄악!!!!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무도 없다. 다시 길을 떠났다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>주인이 몽둥이를 들고 뛰쳐나왔다!!!꺄악!!!!!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_11</t>
+  </si>
+  <si>
+    <t>신비해보이는 책</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>낡은 책이 떨어져있다. \n왠지 신비로워보여..</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>읽어본다. 근데 나 글자를 알았던가..?</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>지나간다. 난 곰이니까!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어떤 마법사의 일기였다. 고백했다 차였다고 한다…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재밌네..</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>저주가 걸려 있었는지 갑자기 어지럽다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">별 거 없겠지, 하고 지나쳤다. </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_12</t>
+  </si>
+  <si>
+    <t>이상한 남자</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>수상한 남자가 말을 걸어온다.\n"거래를 하자곰!"</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래를 수락한다곰.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>무시한다곰.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>꿀단지를 얻었다!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>사기를 당했다! 이쉑!!!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒤에서 이상하게 웃는다. 이상한 사람~</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>남자가 갑자기 뒤에서 덮쳤다. 싸움 끝에 지쳤다… 그냥 사줄걸…</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -608,7 +964,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -719,6 +1075,20 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -842,7 +1212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -917,6 +1287,9 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -925,7 +1298,23 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1181,18 +1570,18 @@
       <c r="E1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="39" t="s">
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="39"/>
     </row>
     <row r="2" spans="1:15" ht="12.75">
       <c r="A2" s="1" t="s">
@@ -1332,7 +1721,7 @@
       <c r="D5" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="36" t="s">
         <v>77</v>
       </c>
       <c r="F5" s="19" t="s">
@@ -1375,7 +1764,7 @@
       <c r="D6" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="36" t="s">
         <v>81</v>
       </c>
       <c r="F6" s="19" t="s">
@@ -1418,7 +1807,7 @@
       <c r="D7" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="36" t="s">
         <v>78</v>
       </c>
       <c r="F7" s="19" t="s">
@@ -1461,7 +1850,7 @@
       <c r="D8" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="40" t="s">
+      <c r="E8" s="36" t="s">
         <v>76</v>
       </c>
       <c r="F8" s="19" t="s">
@@ -1535,103 +1924,248 @@
       <c r="O9" s="5"/>
     </row>
     <row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="A10" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
+      <c r="F10" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="I10" s="21">
+        <v>70</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="M10" s="5">
+        <v>100</v>
+      </c>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="A11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
+      <c r="F11" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="G11" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" s="21">
+        <v>40</v>
+      </c>
+      <c r="J11" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="K11" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="L11" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="M11" s="5">
+        <v>70</v>
+      </c>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
     </row>
     <row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="5"/>
-      <c r="D12" s="18"/>
+      <c r="A12" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
+      <c r="F12" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I12" s="19">
+        <v>45</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="L12" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="M12" s="5">
+        <v>70</v>
+      </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="A13" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>75</v>
+      </c>
       <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
+      <c r="F13" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I13" s="1">
+        <v>65</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="L13" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="M13" s="5">
+        <v>55</v>
+      </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
     </row>
     <row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="29"/>
+      <c r="A14" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>75</v>
+      </c>
       <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
+      <c r="F14" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="G14" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="I14" s="30">
+        <v>55</v>
+      </c>
+      <c r="J14" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="K14" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="M14" s="5">
+        <v>100</v>
+      </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
     </row>
     <row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A15" s="6"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="4"/>
+      <c r="A15" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>75</v>
+      </c>
       <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
+      <c r="F15" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="I15" s="21">
+        <v>40</v>
+      </c>
+      <c r="J15" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="K15" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="L15" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="M15" s="5">
+        <v>70</v>
+      </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
     </row>

--- a/JsonConverter/ExcelFiles/CBAEvent.xlsx
+++ b/JsonConverter/ExcelFiles/CBAEvent.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\CBA\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B6C9B2-E754-4A37-B1E3-437E4A5555F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005043D5-B9E2-4B6B-96BC-261878CB6535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,43 +20,43 @@
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="zgynNiv2YVTupuAxVwKvj3LXvSi69gCaqo2XUeu/LZo="/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="144">
+  <si>
+    <t>Event ID</t>
+  </si>
+  <si>
+    <t>이벤트 제목</t>
+  </si>
+  <si>
+    <t>화면에 출력될 상황 설명</t>
+  </si>
+  <si>
+    <t>BackgroundImageKey</t>
+  </si>
+  <si>
+    <t>NPCPrefabPath</t>
+  </si>
+  <si>
+    <t>선택지1</t>
+  </si>
+  <si>
+    <t>선택지2</t>
+  </si>
   <si>
     <t>string</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
-    <t>Event ID</t>
-  </si>
-  <si>
-    <t>이벤트 제목</t>
-  </si>
-  <si>
-    <t>화면에 출력될 상황 설명</t>
-  </si>
-  <si>
-    <t>NPCPrefabPath</t>
-  </si>
-  <si>
-    <t>선택지1</t>
-  </si>
-  <si>
-    <t>선택지2</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>EventTitle</t>
   </si>
   <si>
@@ -93,21 +93,60 @@
     <t>돌뿌리 발견</t>
   </si>
   <si>
+    <t>걷다가 돌뿌리를 발견했다.\n어엉..?</t>
+  </si>
+  <si>
+    <t>Background</t>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Rock</t>
+  </si>
+  <si>
     <t>점프해서 넘어가볼까?</t>
   </si>
   <si>
+    <t>점프에 성공했다! 촤핫!</t>
+  </si>
+  <si>
+    <t>넘어졌다! \n무릎이 까졌어..</t>
+  </si>
+  <si>
     <t>돌아서 안전하게 가자.</t>
   </si>
   <si>
+    <t>안전하게 돌아갔다! \n안전제일이지!</t>
+  </si>
+  <si>
+    <t>돌아가다 길을 잃었다.. \n나 길치다곰…</t>
+  </si>
+  <si>
     <t>event_2</t>
   </si>
   <si>
     <t>꿀단지 발견</t>
   </si>
   <si>
+    <t>꿀단지를 발견했다. \n침이 흐른다.</t>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_HoneyPot</t>
+  </si>
+  <si>
     <t>맛있게 먹는다. 냠!</t>
   </si>
   <si>
+    <t>기운이 솟는다!! 우어!!!</t>
+  </si>
+  <si>
+    <t>혈당 스파이크… zZZzzzZZ..\n잠에 빠져든다..</t>
+  </si>
+  <si>
+    <t>의심스러워.. 먹지 않는다.</t>
+  </si>
+  <si>
+    <t>현명한 선택이었다곰. \n우리 엄마가 길에 있는 건 먹지 말랬어!</t>
+  </si>
+  <si>
     <t>참다 못해 결국 먹었다..</t>
   </si>
   <si>
@@ -120,321 +159,466 @@
     <t xml:space="preserve">멋진 나무를 발견했다. </t>
   </si>
   <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Tree</t>
+  </si>
+  <si>
     <t>말을 걸어보자.</t>
   </si>
   <si>
+    <t>째려볼 뿐 아무 반응이 없다. \n방해하지 말자…</t>
+  </si>
+  <si>
+    <t>나무에게 말 걸지 말라고 혼났다. \n내향형인가보다…</t>
+  </si>
+  <si>
     <t>밑에서 낮잠을 잔다.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+    <t>그늘이 시원해서 기분이 좋다. \n헷~</t>
+  </si>
+  <si>
+    <t>나무가 저리 가라며 쫓아냈다… \n너무해 엉엉</t>
+  </si>
+  <si>
+    <t>event_4</t>
+  </si>
+  <si>
+    <t>수상한 버섯</t>
+  </si>
+  <si>
+    <t>알록달록한 버섯을 발견했다.\n먹음직스럽기도 하고 수상하기도 하다.</t>
+  </si>
+  <si>
+    <t>NewBackground2048x1536</t>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Mushroom</t>
+  </si>
+  <si>
+    <t>일단 입에 댄다. 난 곰이니까!</t>
+  </si>
+  <si>
+    <t>건강한 버섯이었다.\n난 버섯을 좋아해! 홍홍~</t>
+  </si>
+  <si>
+    <t>배가 꼬르륵 거리며 복통이 느껴진다…\n헉… 뭘 먹은거지?ㅠㅠ</t>
+  </si>
+  <si>
+    <t>그 정도로 멍청하진 않다곰! 냄새만 맡는다.</t>
+  </si>
+  <si>
+    <t>흥! 냄새만 맡고 현명하게 지나쳤다.\n나를 뭐로 보는거야?</t>
+  </si>
+  <si>
+    <t>재채기가 멈추지 않는다...\n푸엑취!우엑취!!!\n훌쩍…</t>
+  </si>
+  <si>
+    <t>event_5</t>
+  </si>
+  <si>
+    <t>길 잃은 아기새</t>
+  </si>
+  <si>
+    <t>나무 아래 아기새 한 마리가 떨어져 있다.\n가엾게 삐약삐약 울고 있다.</t>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_BabyBird</t>
+  </si>
+  <si>
+    <t>둥지에 올려준다.</t>
+  </si>
+  <si>
+    <t>아기새가 안전하게 둥지로 돌아갔다.\n기분이 따뜻해졌다.</t>
+  </si>
+  <si>
+    <t>나무에서 떨어졌다. 엉덩이가 아프다.\n아기새가 한심하게 쳐다본다ㅠㅠ</t>
+  </si>
+  <si>
+    <t>어미새가 근처에 있을거라 믿고 지나친다</t>
+  </si>
+  <si>
+    <t>마음은 무겁고 발걸음은 가볍다. (이거 맞지?)</t>
+  </si>
+  <si>
+    <t>죄책감에 발이 무겁다…\n아기새야 미안해…</t>
+  </si>
+  <si>
+    <t>event_6</t>
+  </si>
+  <si>
+    <t>돼지머리가 왜 여기에</t>
+  </si>
+  <si>
+    <t>길 한복판에 잘린 돼지머리를 발견했다.\n이게 뭐람?</t>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_PigHead</t>
+  </si>
+  <si>
+    <t>입에 전재산 만 원을 물려주고 떠난다.</t>
+  </si>
+  <si>
+    <t>아무 일도 일어나지 않았다.\n내 돈…</t>
+  </si>
+  <si>
+    <t>갑자기 돼지머리가 말을 한다:\n이딴 코딱지를 누굴 줘?\n도로 가져가! 투테퉤!!</t>
+  </si>
+  <si>
+    <t>발로 찬다.</t>
+  </si>
+  <si>
+    <t>돼지머리가 뻥 하고 날아가 사라졌다. 스트레스가 풀렸다.</t>
+  </si>
+  <si>
+    <t>빗나가서 발목을 삐었다… 힘만 썼다…</t>
+  </si>
+  <si>
+    <t>event_7</t>
+  </si>
+  <si>
+    <t>스산한 무덤</t>
+  </si>
+  <si>
+    <t>이름도 없는 낡은 무덤을 발견했다.\n뭔가 묻혀있는 것 같기도 하고…</t>
+  </si>
+  <si>
+    <t>파본다. 난 곰이니까!</t>
+  </si>
+  <si>
+    <t>오래된 사과가 나왔다. 체력+1</t>
+  </si>
+  <si>
+    <t>땅 파다 허리를 삐끗했다.. 크흡…</t>
+  </si>
+  <si>
+    <t>지나간다. 난 무서우니까!</t>
+  </si>
+  <si>
+    <t>뭔가 좋은 게 있었을까…? 아쉽다.</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>event_8</t>
+  </si>
+  <si>
+    <t>떨어진 감자</t>
+  </si>
+  <si>
+    <t>노릇하게 구워진 감자가 길 한복판에 떨어져 있다! 이게 웬 횡재냐!!</t>
+  </si>
+  <si>
+    <t>먹는다. 난 곰이니까!</t>
+  </si>
+  <si>
+    <t>따끈한 감자를 먹었다. 체력 +1</t>
+  </si>
+  <si>
+    <t>오래 돼서 싹 난 감자였다… 독이 올랐다… 엉엉…</t>
+  </si>
+  <si>
+    <t>누굴 거지로 아나? 안 먹는다.</t>
+  </si>
+  <si>
+    <t>배가 고프지만 오늘도 양심을 지켰다...</t>
+  </si>
+  <si>
+    <t>곰이 그런 게 어딨어?! 돌아가서 다시 먹어버렸다. 이거지!</t>
+  </si>
+  <si>
+    <t>event_9</t>
+  </si>
+  <si>
+    <t>모래밭 도착</t>
+  </si>
+  <si>
+    <t>모래밭이 앞을 가로막는다.\n발이 빠질 것 같아…</t>
+  </si>
+  <si>
+    <t>돌진한다. 난 쾌남이니까!</t>
+  </si>
+  <si>
+    <t>오 모래가 생각보다 단단했다. 빠르게 통과했다.</t>
+  </si>
+  <si>
+    <t>발이 빠져 허우적댔다… 나 쾌남 아니다…</t>
+  </si>
+  <si>
+    <t>천천히 조심히 건넌다. (흥…)</t>
+  </si>
+  <si>
+    <t>시간이 걸렸지만 무사히 건넜다.</t>
+  </si>
+  <si>
+    <t>발이 빠져서 지쳐버렸다…</t>
+  </si>
+  <si>
+    <t>event_10</t>
+  </si>
+  <si>
+    <t>빈 집…인가?</t>
+  </si>
+  <si>
+    <t>숲 한 가운데 집이 있다.\n안에서 맛있는 냄새가 난다(!)</t>
+  </si>
+  <si>
+    <t>문을 두드린다.</t>
+  </si>
+  <si>
+    <t>친절한 할머니가 빵을 줬다. 히힛</t>
+  </si>
+  <si>
+    <t>갑자기 문이 열리며 무서운 개가 뛰어나왔다!!!!!! 꺄악!!!!</t>
+  </si>
+  <si>
+    <t>창문으로 몰래 훔쳐본다.</t>
+  </si>
+  <si>
+    <t>아무도 없다. 다시 길을 떠났다.</t>
+  </si>
+  <si>
+    <t>주인이 몽둥이를 들고 뛰쳐나왔다!!!꺄악!!!!!</t>
+  </si>
+  <si>
+    <t>event_11</t>
+  </si>
+  <si>
+    <t>신비해보이는 책</t>
+  </si>
+  <si>
+    <t>낡은 책이 떨어져있다. \n왠지 신비로워보여..</t>
+  </si>
+  <si>
+    <t>읽어본다. 근데 나 글자를 알았던가..?</t>
+  </si>
+  <si>
+    <t>어떤 마법사의 일기였다. 고백했다 차였다고 한다… 재밌네..</t>
+  </si>
+  <si>
+    <t>저주가 걸려 있었는지 갑자기 어지럽다…</t>
+  </si>
+  <si>
+    <t>지나간다. 난 곰이니까!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">별 거 없겠지, 하고 지나쳤다. </t>
+  </si>
+  <si>
+    <t>event_12</t>
+  </si>
+  <si>
+    <t>이상한 남자</t>
+  </si>
+  <si>
+    <t>거래를 수락한다곰.</t>
+  </si>
+  <si>
+    <t>꿀단지를 얻었다!</t>
+  </si>
+  <si>
+    <t>사기를 당했다! 이쉑!!!</t>
+  </si>
+  <si>
+    <t>무시한다곰.</t>
+  </si>
+  <si>
+    <t>뒤에서 이상하게 웃는다. 이상한 사람~</t>
+  </si>
+  <si>
+    <t>남자가 갑자기 뒤에서 덮쳤다. 싸움 끝에 지쳤다… 그냥 사줄걸…</t>
+  </si>
+  <si>
+    <t>event_hat</t>
+  </si>
+  <si>
+    <t>바람에 날린 모자</t>
+  </si>
+  <si>
+    <t>모자를 잡아 돌려준다</t>
+  </si>
+  <si>
+    <t>모자를 써본다</t>
+  </si>
+  <si>
+    <t>꽤 잘 어울린다! 기분이 좋아졌다.
+[곰순이 등장 예정]</t>
+  </si>
+  <si>
+    <t>수상한 남자가 말을 걸어온다.\n"거래를 하자곰!"</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>걷다가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>하늘에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>돌뿌리를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>모자가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>발견했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>날아왔다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.\n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      </rPr>
+      <t xml:space="preserve">.\n
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>어엉</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>어디선가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>..?</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>꿀단지를 발견했다. \n침이 흐른다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>넘어졌다! \n무릎이 까졌어..</t>
-  </si>
-  <si>
-    <t>안전하게 돌아갔다! \n안전제일이지!</t>
-  </si>
-  <si>
-    <t>째려볼 뿐 아무 반응이 없다. \n방해하지 말자…</t>
-  </si>
-  <si>
-    <t>나무에게 말 걸지 말라고 혼났다. \n내향형인가보다…</t>
-  </si>
-  <si>
-    <t>그늘이 시원해서 기분이 좋다. \n헷~</t>
-  </si>
-  <si>
-    <t>의심스러워.. 먹지 않는다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>점프에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>가냘픈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>성공했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>외침이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">! </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>촤핫</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>들린다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>!</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>기운이 솟는다!! 우어!!!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>혈당 스파이크… zZZzzzZZ..\n잠에 빠져든다..</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무가 저리 가라며 쫓아냈다… \n너무해 엉엉</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌아가다 길을 잃었다.. \n나 길치다곰…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>현명한 선택이었다곰. \n우리 엄마가 길에 있는 건 먹지 말랬어!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_4</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>수상한 버섯</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>알록달록한 버섯을 발견했다.\n먹음직스럽기도 하고 수상하기도 하다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>일단 입에 댄다. 난 곰이니까!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>배가 꼬르륵 거리며 복통이 느껴진다…</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>\n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>헉…</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>뭘 먹은거지?ㅠㅠ</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>그 정도로 멍청하진 않다곰! 냄새만 맡는다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      </rPr>
+      <t>.\n
+"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>흥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">! </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>냄새만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>모자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>!"</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>맡고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>고마워하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -443,17 +627,15 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>현명하게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>목소리가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -462,216 +644,33 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>지나쳤다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>들려왔다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>.\n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
+      <t>.
+[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>나를 뭐로 보는거야?</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>재채기가 멈추지 않는다...\n푸엑취!우엑취!!!\n훌쩍…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_5</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>길 잃은 아기새</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 아래 아기새 한 마리가 떨어져 있다.\n가엾게 삐약삐약 울고 있다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>둥지에 올려준다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>아기새가 안전하게 둥지로 돌아갔다.\n기분이 따뜻해졌다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무에서 떨어졌다. 엉덩이가 아프다.\n아기새가 한심하게 쳐다본다ㅠㅠ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>마음은 무겁고 발걸음은 가볍다. (이거 맞지?)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>죄책감에 발이 무겁다…\n아기새야 미안해…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_6</t>
-  </si>
-  <si>
-    <t>돼지머리가 왜 여기에</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>입에 전재산 만 원을 물려주고 떠난다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>길 한복판에 잘린 돼지머리를 발견했다.\n이게 뭐람?</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>발로 찬다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>돼지머리가 뻥 하고 날아가 사라졌다. 스트레스가 풀렸다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>빗나가서 발목을 삐었다… 힘만 썼다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>어미새가 근처에 있을거라 믿고 지나친다</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>갑자기 돼지머리가 말을 한다:\n이딴 코딱지를 누굴 줘?\n도로 가져가! 투테퉤!!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>건강한 버섯이었다.\n난 버섯을 좋아해! 홍홍~</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>아무 일도 일어나지 않았다.\n내 돈…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>BackgroundImageKey</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Background</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>NewBackground2048x1536</t>
-  </si>
-  <si>
-    <t>Prefabs/2D/NPC_CBA/NPC_BabyBird</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/2D/NPC_CBA/NPC_HoneyPot</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/2D/NPC_CBA/NPC_Mushroom</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/2D/NPC_CBA/NPC_PigHead</t>
-  </si>
-  <si>
-    <t>Prefabs/2D/NPC_CBA/NPC_Rock</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/2D/NPC_CBA/NPC_Tree</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_7</t>
-  </si>
-  <si>
-    <t>스산한 무덤</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>이름도 없는 낡은 무덤을 발견했다.\n뭔가 묻혀있는 것 같기도 하고…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>파본다. 난 곰이니까!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>지나간다. 난 무서우니까!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>오래된 사과가 나왔다. 체력+1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>땅 파다 허리를 삐끗했다.. 크흡…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>뭔가 좋은 게 있었을까…? 아쉽다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_8</t>
-  </si>
-  <si>
-    <t>떨어진 감자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>노릇하게 구워진 감자가 길 한복판에 떨어져 있다! 이게 웬 횡재냐!!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>먹는다. 난 곰이니까!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>누굴 거지로 아나? 안 먹는다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="굴림"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>따끈한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>곰순이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -680,17 +679,15 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="굴림"/>
-        <family val="2"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>감자를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>등장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -699,58 +696,52 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="굴림"/>
-        <family val="2"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>먹었다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="굴림"/>
-        <family val="2"/>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>체력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>잡으러</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> +1</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>오래 돼서 싹 난 감자였다…</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>달려가다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -759,17 +750,15 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>독이 올랐다…</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>발을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -778,127 +767,15 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>엉엉…</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>배가 고프지만 오늘도 양심을 지켰다...</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>곰이 그런 게 어딨어?! 돌아가서 다시 먹어버렸다. 이거지!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_9</t>
-  </si>
-  <si>
-    <t>모래밭 도착</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>모래밭이 앞을 가로막는다.\n발이 빠질 것 같아…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌진한다. 난 쾌남이니까!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>천천히 조심히 건넌다. (흥…)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>오 모래가 생각보다 단단했다. 빠르게 통과했다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>시간이 걸렸지만 무사히 건넜다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>발이 빠져 허우적댔다… 나 쾌남 아니다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>발이 빠져서 지쳐버렸다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_10</t>
-  </si>
-  <si>
-    <t>빈 집…인가?</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>숲 한 가운데 집이 있다.\n안에서 맛있는 냄새가 난다(!)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>문을 두드린다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>창문으로 몰래 훔쳐본다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>친절한 할머니가 빵을 줬다. 히힛</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>갑자기 문이 열리며 무서운 개가 뛰어나왔다!!!!!! 꺄악!!!!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>아무도 없다. 다시 길을 떠났다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>주인이 몽둥이를 들고 뛰쳐나왔다!!!꺄악!!!!!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_11</t>
-  </si>
-  <si>
-    <t>신비해보이는 책</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>낡은 책이 떨어져있다. \n왠지 신비로워보여..</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>읽어본다. 근데 나 글자를 알았던가..?</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>지나간다. 난 곰이니까!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>어떤 마법사의 일기였다. 고백했다 차였다고 한다…</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
+      <t>헛디뎌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -907,56 +784,247 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>넘어졌다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
         <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">...\n
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>재밌네..</t>
+      <t>무릎이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>까졌어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..
+[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>곰순이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>저주가 걸려 있었는지 갑자기 어지럽다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">별 거 없겠지, 하고 지나쳤다. </t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_12</t>
-  </si>
-  <si>
-    <t>이상한 남자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>수상한 남자가 말을 걸어온다.\n"거래를 하자곰!"</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>거래를 수락한다곰.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>무시한다곰.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>꿀단지를 얻었다!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>사기를 당했다! 이쉑!!!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>뒤에서 이상하게 웃는다. 이상한 사람~</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>남자가 갑자기 뒤에서 덮쳤다. 싸움 끝에 지쳤다… 그냥 사줄걸…</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주인이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>달려와서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빼어갔다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>민망하다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.
+[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>곰순이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -964,7 +1032,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1044,12 +1112,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
@@ -1089,8 +1151,25 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1145,8 +1224,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8D5F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1208,11 +1292,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1272,50 +1371,59 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1551,74 +1659,75 @@
     <col min="11" max="11" width="33.140625" style="22" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="37.140625" style="3" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="12.5703125" style="3"/>
+    <col min="14" max="14" width="12.5703125" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="19" t="s">
+      <c r="F1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="40" t="s">
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="50"/>
+    </row>
+    <row r="2" spans="1:15" ht="12.75" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="39"/>
-    </row>
-    <row r="2" spans="1:15" ht="12.75">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="B2" s="15" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="25" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>8</v>
@@ -1626,81 +1735,81 @@
     </row>
     <row r="3" spans="1:15" s="12" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" s="20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3" s="26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K3" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M3" s="20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I4" s="21">
         <v>60</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K4" s="18" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="M4" s="5">
         <v>70</v>
@@ -1710,40 +1819,40 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I5" s="22">
         <v>55</v>
       </c>
       <c r="J5" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="19" t="s">
-        <v>45</v>
-      </c>
       <c r="L5" s="23" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="M5" s="5">
         <v>45</v>
@@ -1753,40 +1862,40 @@
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I6" s="22">
         <v>40</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="M6" s="5">
         <v>70</v>
@@ -1796,40 +1905,40 @@
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I7" s="22">
         <v>50</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="L7" s="34" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="M7" s="5">
         <v>55</v>
@@ -1839,28 +1948,28 @@
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>75</v>
-      </c>
       <c r="E8" s="36" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="I8" s="22">
         <v>60</v>
@@ -1869,10 +1978,10 @@
         <v>69</v>
       </c>
       <c r="K8" s="19" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="M8" s="5">
         <v>75</v>
@@ -1882,40 +1991,40 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D9" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="35" t="s">
-        <v>79</v>
-      </c>
       <c r="F9" s="19" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="I9" s="22">
         <v>65</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="M9" s="5">
         <v>60</v>
@@ -1934,23 +2043,23 @@
         <v>84</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="E10" s="21"/>
       <c r="F10" s="24" t="s">
         <v>85</v>
       </c>
       <c r="G10" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="23" t="s">
         <v>87</v>
-      </c>
-      <c r="H10" s="23" t="s">
-        <v>88</v>
       </c>
       <c r="I10" s="21">
         <v>70</v>
       </c>
       <c r="J10" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K10" s="24" t="s">
         <v>89</v>
@@ -1975,28 +2084,28 @@
         <v>93</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="E11" s="21"/>
-      <c r="F11" s="41" t="s">
+      <c r="F11" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="42" t="s">
+      <c r="G11" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="39" t="s">
         <v>96</v>
-      </c>
-      <c r="H11" s="43" t="s">
-        <v>97</v>
       </c>
       <c r="I11" s="21">
         <v>40</v>
       </c>
-      <c r="J11" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="K11" s="44" t="s">
+      <c r="J11" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="K11" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="L11" s="45" t="s">
+      <c r="L11" s="41" t="s">
         <v>99</v>
       </c>
       <c r="M11" s="5">
@@ -2009,33 +2118,33 @@
       <c r="A12" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="42" t="s">
         <v>102</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="E12" s="19"/>
       <c r="F12" s="19" t="s">
         <v>103</v>
       </c>
       <c r="G12" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="I12" s="19">
         <v>45</v>
       </c>
       <c r="J12" s="19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L12" s="23" t="s">
         <v>108</v>
@@ -2057,28 +2166,28 @@
         <v>111</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="I13" s="1">
         <v>65</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L13" s="47" t="s">
+      <c r="L13" s="43" t="s">
         <v>117</v>
       </c>
       <c r="M13" s="5">
@@ -2091,32 +2200,32 @@
       <c r="A14" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="41" t="s">
         <v>119</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="E14" s="30"/>
-      <c r="F14" s="48" t="s">
+      <c r="F14" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="G14" s="49" t="s">
+      <c r="G14" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="H14" s="29" t="s">
         <v>123</v>
-      </c>
-      <c r="H14" s="29" t="s">
-        <v>124</v>
       </c>
       <c r="I14" s="30">
         <v>55</v>
       </c>
-      <c r="J14" s="48" t="s">
-        <v>122</v>
-      </c>
-      <c r="K14" s="48" t="s">
+      <c r="J14" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="K14" s="44" t="s">
         <v>125</v>
       </c>
       <c r="L14" s="5" t="s">
@@ -2136,32 +2245,32 @@
         <v>127</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="E15" s="21"/>
       <c r="F15" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="G15" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="G15" s="14" t="s">
-        <v>131</v>
-      </c>
       <c r="H15" s="17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I15" s="21">
         <v>40</v>
       </c>
       <c r="J15" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="K15" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="K15" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="L15" s="34" t="s">
         <v>133</v>
-      </c>
-      <c r="L15" s="34" t="s">
-        <v>134</v>
       </c>
       <c r="M15" s="5">
         <v>70</v>
@@ -2293,34 +2402,72 @@
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
     </row>
-    <row r="33" spans="1:4" ht="15.75" customHeight="1">
+    <row r="33" spans="1:13" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
     </row>
-    <row r="34" spans="1:4" ht="15.75" customHeight="1">
+    <row r="34" spans="1:13" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
     </row>
-    <row r="35" spans="1:4" ht="15.75" customHeight="1">
+    <row r="35" spans="1:13" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
     </row>
-    <row r="36" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="36" spans="1:13" ht="54.95" customHeight="1">
+      <c r="A36" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="B36" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="C36" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="D36" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="G36" s="52" t="s">
+        <v>141</v>
+      </c>
+      <c r="H36" s="52" t="s">
+        <v>142</v>
+      </c>
+      <c r="I36" s="47">
+        <v>60</v>
+      </c>
+      <c r="J36" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="K36" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="L36" s="52" t="s">
+        <v>143</v>
+      </c>
+      <c r="M36" s="47">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -3275,11 +3422,11 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="J1:M1"/>
     <mergeCell ref="F1:I1"/>
-    <mergeCell ref="J1:M1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/CBAEvent.xlsx
+++ b/JsonConverter/ExcelFiles/CBAEvent.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\CBA\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005043D5-B9E2-4B6B-96BC-261878CB6535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF85FD6-8298-43A9-BAB8-2C4364A085F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="147">
   <si>
     <t>Event ID</t>
   </si>
@@ -198,9 +198,6 @@
     <t>일단 입에 댄다. 난 곰이니까!</t>
   </si>
   <si>
-    <t>건강한 버섯이었다.\n난 버섯을 좋아해! 홍홍~</t>
-  </si>
-  <si>
     <t>배가 꼬르륵 거리며 복통이 느껴진다…\n헉… 뭘 먹은거지?ㅠㅠ</t>
   </si>
   <si>
@@ -258,9 +255,6 @@
     <t>입에 전재산 만 원을 물려주고 떠난다.</t>
   </si>
   <si>
-    <t>아무 일도 일어나지 않았다.\n내 돈…</t>
-  </si>
-  <si>
     <t>갑자기 돼지머리가 말을 한다:\n이딴 코딱지를 누굴 줘?\n도로 가져가! 투테퉤!!</t>
   </si>
   <si>
@@ -366,9 +360,6 @@
     <t>문을 두드린다.</t>
   </si>
   <si>
-    <t>친절한 할머니가 빵을 줬다. 히힛</t>
-  </si>
-  <si>
     <t>갑자기 문이 열리며 무서운 개가 뛰어나왔다!!!!!! 꺄악!!!!</t>
   </si>
   <si>
@@ -412,9 +403,6 @@
   </si>
   <si>
     <t>거래를 수락한다곰.</t>
-  </si>
-  <si>
-    <t>꿀단지를 얻었다!</t>
   </si>
   <si>
     <t>사기를 당했다! 이쉑!!!</t>
@@ -1025,6 +1013,34 @@
       </rPr>
       <t>]</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Choice1HeartsChange</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Choice2HeartsChange</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>건강한 버섯이었다.\n난 버섯을 좋아해! 홍홍~ 체력+1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무 일도 일어나지 않았다.\n내 돈…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>친절한 할머니가 빵을 줬다. 히힛!\n체력+1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>꿀단지를 얻었다! 체력+1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1311,7 +1327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1414,16 +1430,31 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1643,7 +1674,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
+  <dimension ref="A1:Q1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="3" customWidth="1"/>
@@ -1652,18 +1683,20 @@
     <col min="4" max="4" width="26.140625" style="3" customWidth="1"/>
     <col min="5" max="5" width="31.42578125" style="22" customWidth="1"/>
     <col min="6" max="6" width="21.42578125" style="22" customWidth="1"/>
-    <col min="7" max="7" width="24.5703125" style="22" customWidth="1"/>
-    <col min="8" max="8" width="43.28515625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" style="22" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="22" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="33.140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.140625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="19.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="12.5703125" style="3"/>
+    <col min="7" max="7" width="54.42578125" style="22" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" style="22" customWidth="1"/>
+    <col min="9" max="9" width="43.28515625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="45.7109375" style="22" customWidth="1"/>
+    <col min="13" max="13" width="33.140625" style="22" customWidth="1"/>
+    <col min="14" max="14" width="37.140625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="19.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1679,20 +1712,22 @@
       <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="48" t="s">
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
+      <c r="L1" s="50"/>
       <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="51"/>
     </row>
-    <row r="2" spans="1:15" ht="12.75" customHeight="1">
+    <row r="2" spans="1:17" ht="12.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1715,25 +1750,31 @@
         <v>7</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="25" t="s">
         <v>7</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="12" customFormat="1" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" s="12" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>9</v>
       </c>
@@ -1755,26 +1796,32 @@
       <c r="G3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="I3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="J3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="K3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="L3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="M3" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="N3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="20" t="s">
+      <c r="O3" s="20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>20</v>
       </c>
@@ -1796,28 +1843,34 @@
       <c r="G4" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="53">
+        <v>0</v>
+      </c>
+      <c r="I4" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="21">
+      <c r="J4" s="21">
         <v>60</v>
       </c>
-      <c r="J4" s="24" t="s">
+      <c r="K4" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="18" t="s">
+      <c r="L4" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="23" t="s">
+      <c r="M4" s="57">
+        <v>0</v>
+      </c>
+      <c r="N4" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M4" s="5">
+      <c r="O4" s="5">
         <v>70</v>
       </c>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
     </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>31</v>
       </c>
@@ -1839,28 +1892,34 @@
       <c r="G5" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="19">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="22">
+      <c r="J5" s="22">
         <v>55</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="K5" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="L5" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="L5" s="23" t="s">
+      <c r="M5" s="19">
+        <v>0</v>
+      </c>
+      <c r="N5" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="5">
+      <c r="O5" s="5">
         <v>45</v>
       </c>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
     </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>41</v>
       </c>
@@ -1882,28 +1941,34 @@
       <c r="G6" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="19">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="22">
+      <c r="J6" s="22">
         <v>40</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="K6" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="L6" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="23" t="s">
+      <c r="M6" s="19">
+        <v>0</v>
+      </c>
+      <c r="N6" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="5">
+      <c r="O6" s="5">
         <v>70</v>
       </c>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
     </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>51</v>
       </c>
@@ -1923,551 +1988,621 @@
         <v>56</v>
       </c>
       <c r="G7" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="H7" s="19">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="J7" s="22">
+        <v>50</v>
+      </c>
+      <c r="K7" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="I7" s="22">
-        <v>50</v>
-      </c>
-      <c r="J7" s="32" t="s">
+      <c r="L7" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="K7" s="33" t="s">
+      <c r="M7" s="33">
+        <v>0</v>
+      </c>
+      <c r="N7" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="L7" s="34" t="s">
+      <c r="O7" s="5">
+        <v>55</v>
+      </c>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+    </row>
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A8" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="M7" s="5">
-        <v>55</v>
-      </c>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A8" s="4" t="s">
+      <c r="B8" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="C8" s="18" t="s">
         <v>63</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>64</v>
       </c>
       <c r="D8" s="35" t="s">
         <v>54</v>
       </c>
       <c r="E8" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="G8" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="H8" s="19">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="J8" s="22">
+        <v>60</v>
+      </c>
+      <c r="K8" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="22">
-        <v>60</v>
-      </c>
-      <c r="J8" s="19" t="s">
+      <c r="L8" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="K8" s="19" t="s">
+      <c r="M8" s="19">
+        <v>0</v>
+      </c>
+      <c r="N8" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="L8" s="23" t="s">
+      <c r="O8" s="5">
+        <v>75</v>
+      </c>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+    </row>
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A9" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="M8" s="5">
-        <v>75</v>
-      </c>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="C9" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="D9" s="35" t="s">
         <v>54</v>
       </c>
       <c r="E9" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="G9" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="H9" s="19">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="J9" s="22">
+        <v>65</v>
+      </c>
+      <c r="K9" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="L9" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="I9" s="22">
-        <v>65</v>
-      </c>
-      <c r="J9" s="19" t="s">
+      <c r="M9" s="19">
+        <v>0</v>
+      </c>
+      <c r="N9" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="K9" s="19" t="s">
+      <c r="O9" s="5">
+        <v>60</v>
+      </c>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+    </row>
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A10" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="L9" s="23" t="s">
+      <c r="B10" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="M9" s="5">
-        <v>60</v>
-      </c>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-    </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A10" s="4" t="s">
+      <c r="C10" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E10" s="21"/>
       <c r="F10" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="24">
+        <v>1</v>
+      </c>
+      <c r="I10" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="J10" s="21">
+        <v>70</v>
+      </c>
+      <c r="K10" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="L10" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="I10" s="21">
-        <v>70</v>
-      </c>
-      <c r="J10" s="24" t="s">
+      <c r="M10" s="24">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="K10" s="24" t="s">
+      <c r="O10" s="5">
+        <v>100</v>
+      </c>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+    </row>
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A11" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="L10" s="5" t="s">
+      <c r="B11" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="M10" s="5">
-        <v>100</v>
-      </c>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="4" t="s">
+      <c r="C11" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="21"/>
       <c r="F11" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="H11" s="38">
+        <v>1</v>
+      </c>
+      <c r="I11" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="J11" s="21">
+        <v>40</v>
+      </c>
+      <c r="K11" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="H11" s="39" t="s">
+      <c r="L11" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="I11" s="21">
-        <v>40</v>
-      </c>
-      <c r="J11" s="37" t="s">
+      <c r="M11" s="40">
+        <v>0</v>
+      </c>
+      <c r="N11" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="K11" s="40" t="s">
+      <c r="O11" s="5">
+        <v>70</v>
+      </c>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+    </row>
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A12" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="L11" s="41" t="s">
+      <c r="B12" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="M11" s="5">
-        <v>70</v>
-      </c>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-    </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A12" s="4" t="s">
+      <c r="C12" s="42" t="s">
         <v>100</v>
-      </c>
-      <c r="B12" s="41" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>102</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E12" s="19"/>
       <c r="F12" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12" s="19">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="J12" s="19">
+        <v>45</v>
+      </c>
+      <c r="K12" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="L12" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="I12" s="19">
-        <v>45</v>
-      </c>
-      <c r="J12" s="19" t="s">
+      <c r="M12" s="19">
+        <v>0</v>
+      </c>
+      <c r="N12" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="K12" s="19" t="s">
+      <c r="O12" s="5">
+        <v>70</v>
+      </c>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+    </row>
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A13" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="L12" s="23" t="s">
+      <c r="B13" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="M12" s="5">
-        <v>70</v>
-      </c>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A13" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="D13" s="35" t="s">
         <v>54</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J13" s="1">
+        <v>65</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="I13" s="1">
-        <v>65</v>
-      </c>
-      <c r="J13" s="1" t="s">
+      <c r="O13" s="5">
+        <v>55</v>
+      </c>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+    </row>
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A14" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="B14" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="L13" s="43" t="s">
+      <c r="C14" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="M13" s="5">
-        <v>55</v>
-      </c>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A14" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B14" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="D14" s="35" t="s">
         <v>54</v>
       </c>
       <c r="E14" s="30"/>
       <c r="F14" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="G14" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="H14" s="45">
+        <v>0</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="J14" s="30">
+        <v>55</v>
+      </c>
+      <c r="K14" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="G14" s="45" t="s">
+      <c r="L14" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="H14" s="29" t="s">
+      <c r="M14" s="44">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="O14" s="5">
+        <v>100</v>
+      </c>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+    </row>
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A15" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="I14" s="30">
-        <v>55</v>
-      </c>
-      <c r="J14" s="44" t="s">
+      <c r="B15" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="K14" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="M14" s="5">
-        <v>100</v>
-      </c>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-    </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A15" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>127</v>
-      </c>
       <c r="C15" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D15" s="35" t="s">
         <v>54</v>
       </c>
       <c r="E15" s="21"/>
       <c r="F15" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="H15" s="52">
+        <v>1</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J15" s="21">
+        <v>40</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="L15" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="M15" s="37">
+        <v>0</v>
+      </c>
+      <c r="N15" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="H15" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="I15" s="21">
-        <v>40</v>
-      </c>
-      <c r="J15" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="K15" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="L15" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="M15" s="5">
+      <c r="O15" s="5">
         <v>70</v>
       </c>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
     </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="4"/>
       <c r="C16" s="31"/>
       <c r="D16" s="6"/>
       <c r="E16" s="21"/>
       <c r="F16" s="21"/>
       <c r="G16" s="21"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="6"/>
       <c r="J16" s="21"/>
       <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
     </row>
-    <row r="17" spans="1:11" ht="15.75" customHeight="1">
+    <row r="17" spans="1:13" ht="15.75" customHeight="1">
       <c r="A17" s="4"/>
       <c r="C17" s="31"/>
       <c r="D17" s="6"/>
       <c r="E17" s="21"/>
       <c r="F17" s="21"/>
       <c r="G17" s="21"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="6"/>
       <c r="J17" s="21"/>
       <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
     </row>
-    <row r="18" spans="1:11" ht="15.75" customHeight="1">
+    <row r="18" spans="1:13" ht="15.75" customHeight="1">
       <c r="A18" s="8"/>
       <c r="C18" s="18"/>
       <c r="D18" s="6"/>
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
       <c r="G18" s="21"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="6"/>
       <c r="J18" s="21"/>
       <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
     </row>
-    <row r="19" spans="1:11" ht="15.75" customHeight="1">
+    <row r="19" spans="1:13" ht="15.75" customHeight="1">
       <c r="A19" s="8"/>
       <c r="C19" s="4"/>
       <c r="D19" s="7"/>
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
       <c r="G19" s="21"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="23"/>
       <c r="J19" s="21"/>
       <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="21"/>
     </row>
-    <row r="20" spans="1:11" ht="15.75" customHeight="1">
+    <row r="20" spans="1:13" ht="15.75" customHeight="1">
       <c r="A20" s="8"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
       <c r="G20" s="21"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="5"/>
       <c r="J20" s="21"/>
       <c r="K20" s="21"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:11" ht="15.75" customHeight="1">
+    <row r="21" spans="1:13" ht="15.75" customHeight="1">
       <c r="A21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
     </row>
-    <row r="22" spans="1:11" ht="15.75" customHeight="1">
+    <row r="22" spans="1:13" ht="15.75" customHeight="1">
       <c r="A22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
     </row>
-    <row r="23" spans="1:11" ht="15.75" customHeight="1">
+    <row r="23" spans="1:13" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
     </row>
-    <row r="24" spans="1:11" ht="15.75" customHeight="1">
+    <row r="24" spans="1:13" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
     </row>
-    <row r="25" spans="1:11" ht="15.75" customHeight="1">
+    <row r="25" spans="1:13" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="F25" s="21"/>
     </row>
-    <row r="26" spans="1:11" ht="15.75" customHeight="1">
+    <row r="26" spans="1:13" ht="15.75" customHeight="1">
       <c r="A26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="F26" s="21"/>
     </row>
-    <row r="27" spans="1:11" ht="15.75" customHeight="1">
+    <row r="27" spans="1:13" ht="15.75" customHeight="1">
       <c r="A27" s="9"/>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="F27" s="21"/>
     </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1">
+    <row r="28" spans="1:13" ht="15.75" customHeight="1">
       <c r="A28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="F28" s="21"/>
     </row>
-    <row r="29" spans="1:11" ht="15.75" customHeight="1">
+    <row r="29" spans="1:13" ht="15.75" customHeight="1">
       <c r="A29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
     </row>
-    <row r="30" spans="1:11" ht="15.75" customHeight="1">
+    <row r="30" spans="1:13" ht="15.75" customHeight="1">
       <c r="A30" s="9"/>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
     </row>
-    <row r="31" spans="1:11" ht="15.75" customHeight="1">
+    <row r="31" spans="1:13" ht="15.75" customHeight="1">
       <c r="A31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
     </row>
-    <row r="32" spans="1:11" ht="15.75" customHeight="1">
+    <row r="32" spans="1:13" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
     </row>
-    <row r="33" spans="1:13" ht="15.75" customHeight="1">
+    <row r="33" spans="1:15" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
     </row>
-    <row r="34" spans="1:13" ht="15.75" customHeight="1">
+    <row r="34" spans="1:15" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
     </row>
-    <row r="35" spans="1:13" ht="15.75" customHeight="1">
+    <row r="35" spans="1:15" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
     </row>
-    <row r="36" spans="1:13" ht="54.95" customHeight="1">
+    <row r="36" spans="1:15" ht="54.95" customHeight="1">
       <c r="A36" s="46" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B36" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="C36" s="52" t="s">
-        <v>140</v>
+        <v>131</v>
+      </c>
+      <c r="C36" s="48" t="s">
+        <v>136</v>
       </c>
       <c r="D36" s="47" t="s">
         <v>54</v>
       </c>
       <c r="E36" s="47"/>
       <c r="F36" s="47" t="s">
-        <v>136</v>
-      </c>
-      <c r="G36" s="52" t="s">
-        <v>141</v>
-      </c>
-      <c r="H36" s="52" t="s">
-        <v>142</v>
-      </c>
-      <c r="I36" s="47">
+        <v>132</v>
+      </c>
+      <c r="G36" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="H36" s="48">
+        <v>0</v>
+      </c>
+      <c r="I36" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="J36" s="47">
         <v>60</v>
       </c>
-      <c r="J36" s="47" t="s">
-        <v>137</v>
-      </c>
       <c r="K36" s="47" t="s">
-        <v>138</v>
-      </c>
-      <c r="L36" s="52" t="s">
-        <v>143</v>
+        <v>133</v>
+      </c>
+      <c r="L36" s="47" t="s">
+        <v>134</v>
       </c>
       <c r="M36" s="47">
+        <v>0</v>
+      </c>
+      <c r="N36" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="O36" s="47">
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:15" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -3422,8 +3557,8 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="K1:O1"/>
+    <mergeCell ref="F1:J1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/JsonConverter/ExcelFiles/CBAEvent.xlsx
+++ b/JsonConverter/ExcelFiles/CBAEvent.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\CBA\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF85FD6-8298-43A9-BAB8-2C4364A085F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{624749A7-AC5D-4878-9809-457F6C89FE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14950" yWindow="1570" windowWidth="14860" windowHeight="12440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CBAEvent" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="195">
   <si>
     <t>Event ID</t>
   </si>
@@ -1041,6 +1041,193 @@
   </si>
   <si>
     <t>꿀단지를 얻었다! 체력+1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_13</t>
+  </si>
+  <si>
+    <t>event_14</t>
+  </si>
+  <si>
+    <t>event_15</t>
+  </si>
+  <si>
+    <t>귀여운 여우</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>부드러워 보이는 털을 가진 여우가 나타났다!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Fox</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>친구가 되자고 한다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>여우는 도도하게 고개를 홱 돌리고 가버렸다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>여우가 다가와 머리를 한 번 부비고 갔다. 부드러워,,,</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>물면 어떡해!! 그냥 갈래.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>여우가 먼저 도망갔다. 쳇~</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>여우가 왁!! 하고 달려들었다. 우엉 ㅠㅠ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_DinoEgg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>커다란 공룡알</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅇㄹㅇㄹㅇㄹㅇㄹ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅇㄹㅇㄹ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅇㄹㅇㄹㅇㄹ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅇㄹㅇㄹㅇㄹㅇㄹㅇㄹ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Frog</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>독개구리</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>독독</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅊㄴㅊㄴ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅊㄴㅊ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅊㄴㅊㄴㅊㄴ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅊㄴㅊㄴㅊ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_16</t>
+  </si>
+  <si>
+    <t>event_17</t>
+  </si>
+  <si>
+    <t>NewBackground2048x1536</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Fireplace</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>모닥불</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅇㄹㄴㅇ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅇㄹ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅇㄹㄴㅇㄹ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅇㄹㄴ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㄴㄷㄹㅇ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>야구빠따</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>어떤 정신머리 나간 야구선수가 지 목숨과도 같은 야구빠따를 놓고 갔어?!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_BaseballBat</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdse</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㄷㄹㄴㅇㄹ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅇㄹㄷ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅇㄹㄷㄴ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Tomb</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Potato</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Sand</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_House</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Book</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Wizard</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1393,7 +1580,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1433,29 +1619,30 @@
     <xf numFmtId="0" fontId="19" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1712,20 +1899,20 @@
       <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="55" t="s">
+      <c r="F1" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
       <c r="J1" s="56"/>
-      <c r="K1" s="49" t="s">
+      <c r="K1" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="51"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="53"/>
     </row>
     <row r="2" spans="1:17" ht="12.75" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -1843,7 +2030,7 @@
       <c r="G4" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="53">
+      <c r="H4" s="49">
         <v>0</v>
       </c>
       <c r="I4" s="16" t="s">
@@ -1858,7 +2045,7 @@
       <c r="L4" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="57">
+      <c r="M4" s="50">
         <v>0</v>
       </c>
       <c r="N4" s="23" t="s">
@@ -1883,7 +2070,7 @@
       <c r="D5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="35" t="s">
         <v>34</v>
       </c>
       <c r="F5" s="19" t="s">
@@ -1932,7 +2119,7 @@
       <c r="D6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="35" t="s">
         <v>44</v>
       </c>
       <c r="F6" s="19" t="s">
@@ -1978,10 +2165,10 @@
       <c r="C7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="35" t="s">
         <v>55</v>
       </c>
       <c r="F7" s="19" t="s">
@@ -1999,16 +2186,16 @@
       <c r="J7" s="22">
         <v>50</v>
       </c>
-      <c r="K7" s="32" t="s">
+      <c r="K7" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="L7" s="33" t="s">
+      <c r="L7" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="M7" s="33">
+      <c r="M7" s="32">
         <v>0</v>
       </c>
-      <c r="N7" s="34" t="s">
+      <c r="N7" s="33" t="s">
         <v>60</v>
       </c>
       <c r="O7" s="5">
@@ -2021,16 +2208,16 @@
       <c r="A8" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="33" t="s">
         <v>62</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="35" t="s">
         <v>64</v>
       </c>
       <c r="F8" s="19" t="s">
@@ -2076,10 +2263,10 @@
       <c r="C9" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="34" t="s">
         <v>74</v>
       </c>
       <c r="F9" s="19" t="s">
@@ -2128,7 +2315,9 @@
       <c r="D10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="21"/>
+      <c r="E10" s="21" t="s">
+        <v>189</v>
+      </c>
       <c r="F10" s="24" t="s">
         <v>83</v>
       </c>
@@ -2175,32 +2364,34 @@
       <c r="D11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="21"/>
-      <c r="F11" s="37" t="s">
+      <c r="E11" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="F11" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="G11" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="H11" s="38">
+      <c r="H11" s="37">
         <v>1</v>
       </c>
-      <c r="I11" s="39" t="s">
+      <c r="I11" s="38" t="s">
         <v>94</v>
       </c>
       <c r="J11" s="21">
         <v>40</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="K11" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="L11" s="40" t="s">
+      <c r="L11" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="M11" s="40">
+      <c r="M11" s="39">
         <v>0</v>
       </c>
-      <c r="N11" s="41" t="s">
+      <c r="N11" s="40" t="s">
         <v>97</v>
       </c>
       <c r="O11" s="5">
@@ -2213,16 +2404,18 @@
       <c r="A12" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="41" t="s">
         <v>100</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="19"/>
+      <c r="E12" s="21" t="s">
+        <v>191</v>
+      </c>
       <c r="F12" s="19" t="s">
         <v>101</v>
       </c>
@@ -2266,10 +2459,12 @@
       <c r="C13" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="35" t="s">
+      <c r="D13" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="1"/>
+      <c r="E13" s="21" t="s">
+        <v>192</v>
+      </c>
       <c r="F13" s="1" t="s">
         <v>110</v>
       </c>
@@ -2294,7 +2489,7 @@
       <c r="M13" s="1">
         <v>0</v>
       </c>
-      <c r="N13" s="43" t="s">
+      <c r="N13" s="42" t="s">
         <v>114</v>
       </c>
       <c r="O13" s="5">
@@ -2307,23 +2502,25 @@
       <c r="A14" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="40" t="s">
         <v>116</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D14" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="44" t="s">
+      <c r="D14" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F14" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="G14" s="45" t="s">
+      <c r="G14" s="44" t="s">
         <v>119</v>
       </c>
-      <c r="H14" s="45">
+      <c r="H14" s="44">
         <v>0</v>
       </c>
       <c r="I14" s="29" t="s">
@@ -2332,13 +2529,13 @@
       <c r="J14" s="30">
         <v>55</v>
       </c>
-      <c r="K14" s="44" t="s">
+      <c r="K14" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="L14" s="44" t="s">
+      <c r="L14" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="M14" s="44">
+      <c r="M14" s="43">
         <v>0</v>
       </c>
       <c r="N14" s="5" t="s">
@@ -2354,23 +2551,25 @@
       <c r="A15" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B15" s="34" t="s">
+      <c r="B15" s="33" t="s">
         <v>124</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="21"/>
+      <c r="E15" s="21" t="s">
+        <v>194</v>
+      </c>
       <c r="F15" s="24" t="s">
         <v>125</v>
       </c>
       <c r="G15" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="H15" s="52">
+      <c r="H15" s="48">
         <v>1</v>
       </c>
       <c r="I15" s="17" t="s">
@@ -2382,13 +2581,13 @@
       <c r="K15" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="L15" s="37" t="s">
+      <c r="L15" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="M15" s="37">
+      <c r="M15" s="36">
         <v>0</v>
       </c>
-      <c r="N15" s="34" t="s">
+      <c r="N15" s="33" t="s">
         <v>129</v>
       </c>
       <c r="O15" s="5">
@@ -2398,135 +2597,300 @@
       <c r="Q15" s="5"/>
     </row>
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A16" s="4"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
+      <c r="A16" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" s="57" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="H16" s="21">
+        <v>0</v>
+      </c>
+      <c r="I16" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="J16" s="21">
+        <v>30</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="L16" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="M16" s="21">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="O16" s="3">
+        <v>70</v>
+      </c>
     </row>
-    <row r="17" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A17" s="4"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
+    <row r="17" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A17" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="57" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="H17" s="21">
+        <v>1</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="J17" s="21">
+        <v>65</v>
+      </c>
+      <c r="K17" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="L17" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="M17" s="21">
+        <v>0</v>
+      </c>
+      <c r="N17" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="O17" s="3">
+        <v>80</v>
+      </c>
     </row>
-    <row r="18" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A18" s="8"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
+    <row r="18" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A18" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="F18" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="G18" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="H18" s="21">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="J18" s="21">
+        <v>75</v>
+      </c>
+      <c r="K18" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="L18" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="M18" s="21">
+        <v>1</v>
+      </c>
+      <c r="N18" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="O18" s="3">
+        <v>65</v>
+      </c>
     </row>
-    <row r="19" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21"/>
+    <row r="19" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A19" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D19" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="F19" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="G19" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="H19" s="21">
+        <v>1</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="J19" s="21">
+        <v>80</v>
+      </c>
+      <c r="K19" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="L19" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="M19" s="21">
+        <v>1</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="O19" s="3">
+        <v>55</v>
+      </c>
     </row>
-    <row r="20" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
+    <row r="20" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A20" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="G20" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="H20" s="21">
+        <v>0</v>
+      </c>
+      <c r="I20" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="J20" s="21">
+        <v>60</v>
+      </c>
+      <c r="K20" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="L20" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="M20" s="21">
+        <v>1</v>
+      </c>
+      <c r="N20" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="O20" s="3">
+        <v>60</v>
+      </c>
     </row>
-    <row r="21" spans="1:13" ht="15.75" customHeight="1">
+    <row r="21" spans="1:15" ht="15.75" customHeight="1">
       <c r="A21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
     </row>
-    <row r="22" spans="1:13" ht="15.75" customHeight="1">
+    <row r="22" spans="1:15" ht="15.75" customHeight="1">
       <c r="A22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
     </row>
-    <row r="23" spans="1:13" ht="15.75" customHeight="1">
+    <row r="23" spans="1:15" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
     </row>
-    <row r="24" spans="1:13" ht="15.75" customHeight="1">
+    <row r="24" spans="1:15" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
     </row>
-    <row r="25" spans="1:13" ht="15.75" customHeight="1">
+    <row r="25" spans="1:15" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="F25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="15.75" customHeight="1">
+    <row r="26" spans="1:15" ht="15.75" customHeight="1">
       <c r="A26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="F26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="15.75" customHeight="1">
+    <row r="27" spans="1:15" ht="15.75" customHeight="1">
       <c r="A27" s="9"/>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="F27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="15.75" customHeight="1">
+    <row r="28" spans="1:15" ht="15.75" customHeight="1">
       <c r="A28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="F28" s="21"/>
     </row>
-    <row r="29" spans="1:13" ht="15.75" customHeight="1">
+    <row r="29" spans="1:15" ht="15.75" customHeight="1">
       <c r="A29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
     </row>
-    <row r="30" spans="1:13" ht="15.75" customHeight="1">
+    <row r="30" spans="1:15" ht="15.75" customHeight="1">
       <c r="A30" s="9"/>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
     </row>
-    <row r="31" spans="1:13" ht="15.75" customHeight="1">
+    <row r="31" spans="1:15" ht="15.75" customHeight="1">
       <c r="A31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
     </row>
-    <row r="32" spans="1:13" ht="15.75" customHeight="1">
+    <row r="32" spans="1:15" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
@@ -2547,47 +2911,47 @@
       <c r="D35" s="10"/>
     </row>
     <row r="36" spans="1:15" ht="54.95" customHeight="1">
-      <c r="A36" s="46" t="s">
+      <c r="A36" s="45" t="s">
         <v>130</v>
       </c>
-      <c r="B36" s="46" t="s">
+      <c r="B36" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="C36" s="48" t="s">
+      <c r="C36" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="D36" s="47" t="s">
+      <c r="D36" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47" t="s">
+      <c r="E36" s="46"/>
+      <c r="F36" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="G36" s="48" t="s">
+      <c r="G36" s="47" t="s">
         <v>137</v>
       </c>
-      <c r="H36" s="48">
+      <c r="H36" s="47">
         <v>0</v>
       </c>
-      <c r="I36" s="48" t="s">
+      <c r="I36" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="J36" s="47">
+      <c r="J36" s="46">
         <v>60</v>
       </c>
-      <c r="K36" s="47" t="s">
+      <c r="K36" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="L36" s="47" t="s">
+      <c r="L36" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="M36" s="47">
+      <c r="M36" s="46">
         <v>0</v>
       </c>
-      <c r="N36" s="48" t="s">
+      <c r="N36" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="O36" s="47">
+      <c r="O36" s="46">
         <v>80</v>
       </c>
     </row>

--- a/JsonConverter/ExcelFiles/CBAEvent.xlsx
+++ b/JsonConverter/ExcelFiles/CBAEvent.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\CBA\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{624749A7-AC5D-4878-9809-457F6C89FE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A974DEA-CD8D-4068-B202-E4C84009518E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14950" yWindow="1570" windowWidth="14860" windowHeight="12440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7050" yWindow="1695" windowWidth="19590" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CBAEvent" sheetId="1" r:id="rId1"/>
@@ -1628,6 +1628,7 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1642,7 +1643,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1899,20 +1899,20 @@
       <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="51" t="s">
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="54"/>
     </row>
     <row r="2" spans="1:17" ht="12.75" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -2080,7 +2080,7 @@
         <v>36</v>
       </c>
       <c r="H5" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>37</v>
@@ -2603,7 +2603,7 @@
       <c r="B16" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C16" s="57" t="s">
+      <c r="C16" s="51" t="s">
         <v>151</v>
       </c>
       <c r="D16" s="4" t="s">
@@ -2650,7 +2650,7 @@
       <c r="B17" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="57" t="s">
+      <c r="C17" s="51" t="s">
         <v>161</v>
       </c>
       <c r="D17" s="4" t="s">

--- a/JsonConverter/ExcelFiles/CBAEvent.xlsx
+++ b/JsonConverter/ExcelFiles/CBAEvent.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\CBA\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A974DEA-CD8D-4068-B202-E4C84009518E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9568A3E-366F-4D2D-AF09-A0FAB5B1E778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7050" yWindow="1695" windowWidth="19590" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CBAEvent" sheetId="1" r:id="rId1"/>
@@ -429,11 +429,222 @@
     <t>모자를 써본다</t>
   </si>
   <si>
-    <t>꽤 잘 어울린다! 기분이 좋아졌다.
-[곰순이 등장 예정]</t>
-  </si>
-  <si>
     <t>수상한 남자가 말을 걸어온다.\n"거래를 하자곰!"</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Choice1HeartsChange</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Choice2HeartsChange</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>건강한 버섯이었다.\n난 버섯을 좋아해! 홍홍~ 체력+1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무 일도 일어나지 않았다.\n내 돈…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>친절한 할머니가 빵을 줬다. 히힛!\n체력+1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>꿀단지를 얻었다! 체력+1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_13</t>
+  </si>
+  <si>
+    <t>event_14</t>
+  </si>
+  <si>
+    <t>event_15</t>
+  </si>
+  <si>
+    <t>귀여운 여우</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>부드러워 보이는 털을 가진 여우가 나타났다!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Fox</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>친구가 되자고 한다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>여우는 도도하게 고개를 홱 돌리고 가버렸다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>여우가 다가와 머리를 한 번 부비고 갔다. 부드러워,,,</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>물면 어떡해!! 그냥 갈래.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>여우가 먼저 도망갔다. 쳇~</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>여우가 왁!! 하고 달려들었다. 우엉 ㅠㅠ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_DinoEgg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>커다란 공룡알</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅇㄹㅇㄹㅇㄹㅇㄹ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅇㄹㅇㄹ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅇㄹㅇㄹㅇㄹ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅇㄹㅇㄹㅇㄹㅇㄹㅇㄹ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Frog</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>독개구리</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>독독</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅊㄴㅊㄴ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅊㄴㅊ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅊㄴㅊㄴㅊㄴ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅊㄴㅊㄴㅊ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_16</t>
+  </si>
+  <si>
+    <t>event_17</t>
+  </si>
+  <si>
+    <t>NewBackground2048x1536</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Fireplace</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>모닥불</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅇㄹㄴㅇ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅇㄹ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅇㄹㄴㅇㄹ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅇㄹㄴ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㄴㄷㄹㅇ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>야구빠따</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>어떤 정신머리 나간 야구선수가 지 목숨과도 같은 야구빠따를 놓고 갔어?!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_BaseballBat</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdse</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㄷㄹㄴㅇㄹ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅇㄹㄷ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅇㄹㄷㄴ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Tomb</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Potato</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Sand</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_House</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Book</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/NPC_CBA/NPC_Wizard</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -444,7 +655,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>하늘에서</t>
+      <t>고마워하는</t>
     </r>
     <r>
       <rPr>
@@ -461,7 +672,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>모자가</t>
+      <t>목소리가</t>
     </r>
     <r>
       <rPr>
@@ -478,7 +689,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>날아왔다</t>
+      <t>들려왔다</t>
     </r>
     <r>
       <rPr>
@@ -486,9 +697,11 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">.\n
-</t>
-    </r>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -496,7 +709,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>어디선가</t>
+      <t>잡으러</t>
     </r>
     <r>
       <rPr>
@@ -513,7 +726,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>가냘픈</t>
+      <t>달려가다</t>
     </r>
     <r>
       <rPr>
@@ -530,7 +743,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>외침이</t>
+      <t>발을</t>
     </r>
     <r>
       <rPr>
@@ -547,7 +760,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>들린다</t>
+      <t>헛디뎌</t>
     </r>
     <r>
       <rPr>
@@ -555,8 +768,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>.\n
-"</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -565,7 +777,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>내</t>
+      <t>넘어졌다</t>
     </r>
     <r>
       <rPr>
@@ -573,7 +785,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t>...\n</t>
     </r>
     <r>
       <rPr>
@@ -582,7 +794,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>모자</t>
+      <t>무릎이</t>
     </r>
     <r>
       <rPr>
@@ -590,11 +802,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>!"</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
+      <t xml:space="preserve"> </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -602,7 +811,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>고마워하는</t>
+      <t>까졌어</t>
     </r>
     <r>
       <rPr>
@@ -610,8 +819,20 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
+      <t>..</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흑흑..</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -619,7 +840,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>목소리가</t>
+      <t>꽤</t>
     </r>
     <r>
       <rPr>
@@ -636,7 +857,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>들려왔다</t>
+      <t>잘</t>
     </r>
     <r>
       <rPr>
@@ -644,8 +865,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>.
-[</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -654,7 +874,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>곰순이</t>
+      <t>어울린다</t>
     </r>
     <r>
       <rPr>
@@ -662,7 +882,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">! </t>
     </r>
     <r>
       <rPr>
@@ -671,7 +891,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>등장</t>
+      <t>기분이</t>
     </r>
     <r>
       <rPr>
@@ -688,7 +908,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>예정</t>
+      <t>좋아졌다</t>
     </r>
     <r>
       <rPr>
@@ -696,7 +916,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>]</t>
+      <t>.</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -708,7 +928,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>잡으러</t>
+      <t>모자</t>
     </r>
     <r>
       <rPr>
@@ -725,7 +945,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>달려가다</t>
+      <t>주인이</t>
     </r>
     <r>
       <rPr>
@@ -742,7 +962,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>발을</t>
+      <t>달려와서</t>
     </r>
     <r>
       <rPr>
@@ -751,6 +971,15 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모자를 받아</t>
     </r>
     <r>
       <rPr>
@@ -759,7 +988,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>헛디뎌</t>
+      <t>갔다</t>
     </r>
     <r>
       <rPr>
@@ -767,7 +996,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -776,7 +1005,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>넘어졌다</t>
+      <t>민망하다</t>
     </r>
     <r>
       <rPr>
@@ -784,9 +1013,11 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">...\n
-</t>
-    </r>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -794,7 +1025,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>무릎이</t>
+      <t>하늘에서</t>
     </r>
     <r>
       <rPr>
@@ -811,7 +1042,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>까졌어</t>
+      <t>모자가</t>
     </r>
     <r>
       <rPr>
@@ -819,8 +1050,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>..
-[</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -829,7 +1059,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>곰순이</t>
+      <t>날아왔다</t>
     </r>
     <r>
       <rPr>
@@ -837,7 +1067,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -846,7 +1076,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>등장</t>
+      <t>어디선가 가냘픈</t>
     </r>
     <r>
       <rPr>
@@ -854,7 +1084,16 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">왠지 예쁜 것 같은) </t>
     </r>
     <r>
       <rPr>
@@ -863,7 +1102,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>예정</t>
+      <t>외침이</t>
     </r>
     <r>
       <rPr>
@@ -871,11 +1110,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>]</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
+      <t xml:space="preserve"> </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -883,7 +1119,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>모자</t>
+      <t>들린다</t>
     </r>
     <r>
       <rPr>
@@ -891,7 +1127,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t>. "</t>
     </r>
     <r>
       <rPr>
@@ -900,7 +1136,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>주인이</t>
+      <t>내</t>
     </r>
     <r>
       <rPr>
@@ -917,7 +1153,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>달려와서</t>
+      <t>모자</t>
     </r>
     <r>
       <rPr>
@@ -925,309 +1161,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>빼어갔다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>민망하다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.
-[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>곰순이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>예정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>]</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Choice1HeartsChange</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Choice2HeartsChange</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>건강한 버섯이었다.\n난 버섯을 좋아해! 홍홍~ 체력+1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>아무 일도 일어나지 않았다.\n내 돈…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>친절한 할머니가 빵을 줬다. 히힛!\n체력+1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>꿀단지를 얻었다! 체력+1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_13</t>
-  </si>
-  <si>
-    <t>event_14</t>
-  </si>
-  <si>
-    <t>event_15</t>
-  </si>
-  <si>
-    <t>귀여운 여우</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>부드러워 보이는 털을 가진 여우가 나타났다!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/2D/NPC_CBA/NPC_Fox</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>친구가 되자고 한다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>여우는 도도하게 고개를 홱 돌리고 가버렸다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>여우가 다가와 머리를 한 번 부비고 갔다. 부드러워,,,</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>물면 어떡해!! 그냥 갈래.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>여우가 먼저 도망갔다. 쳇~</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>여우가 왁!! 하고 달려들었다. 우엉 ㅠㅠ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/2D/NPC_CBA/NPC_DinoEgg</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>커다란 공룡알</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㅇㄹㅇㄹㅇㄹㅇㄹ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㅇㄹㅇㄹ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㅇㄹㅇㄹㅇㄹ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㅇㄹㅇㄹㅇㄹㅇㄹㅇㄹ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/2D/NPC_CBA/NPC_Frog</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>독개구리</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>독독</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅊㄴㅊㄴ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅊㄴㅊ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅊㄴㅊㄴㅊㄴ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅊㄴㅊㄴㅊ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_16</t>
-  </si>
-  <si>
-    <t>event_17</t>
-  </si>
-  <si>
-    <t>NewBackground2048x1536</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/2D/NPC_CBA/NPC_Fireplace</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>모닥불</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㅇㄹㄴㅇ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅇㄹ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅇㄹㄴㅇㄹ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅇㄹㄴ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㄴㄷㄹㅇ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>야구빠따</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>어떤 정신머리 나간 야구선수가 지 목숨과도 같은 야구빠따를 놓고 갔어?!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/2D/NPC_CBA/NPC_BaseballBat</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdse</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㄷㄹㄴㅇㄹ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅇㄹㄷ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅇㄹㄷㄴ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/2D/NPC_CBA/NPC_Tomb</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/2D/NPC_CBA/NPC_Potato</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/2D/NPC_CBA/NPC_Sand</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/2D/NPC_CBA/NPC_House</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/2D/NPC_CBA/NPC_Book</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/2D/NPC_CBA/NPC_Wizard</t>
+      <t>!"</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1235,7 +1170,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1369,6 +1304,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -1937,7 +1878,7 @@
         <v>7</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>7</v>
@@ -1952,7 +1893,7 @@
         <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>7</v>
@@ -1984,7 +1925,7 @@
         <v>13</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>14</v>
@@ -1999,7 +1940,7 @@
         <v>17</v>
       </c>
       <c r="M3" s="20" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="N3" s="11" t="s">
         <v>18</v>
@@ -2175,7 +2116,7 @@
         <v>56</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H7" s="19">
         <v>1</v>
@@ -2273,7 +2214,7 @@
         <v>75</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="H9" s="19">
         <v>0</v>
@@ -2316,7 +2257,7 @@
         <v>23</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F10" s="24" t="s">
         <v>83</v>
@@ -2365,7 +2306,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F11" s="36" t="s">
         <v>92</v>
@@ -2414,7 +2355,7 @@
         <v>23</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F12" s="19" t="s">
         <v>101</v>
@@ -2463,13 +2404,13 @@
         <v>54</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H13" s="1">
         <v>1</v>
@@ -2509,10 +2450,10 @@
         <v>117</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F14" s="43" t="s">
         <v>118</v>
@@ -2555,19 +2496,19 @@
         <v>124</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D15" s="34" t="s">
         <v>54</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F15" s="24" t="s">
         <v>125</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="H15" s="48">
         <v>1</v>
@@ -2598,46 +2539,46 @@
     </row>
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H16" s="21">
         <v>0</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="J16" s="21">
         <v>30</v>
       </c>
       <c r="K16" s="24" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="L16" s="24" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="M16" s="21">
         <v>0</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="O16" s="3">
         <v>70</v>
@@ -2645,46 +2586,46 @@
     </row>
     <row r="17" spans="1:15" ht="15.75" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H17" s="21">
         <v>1</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="J17" s="21">
         <v>65</v>
       </c>
       <c r="K17" s="36" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="L17" s="36" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="M17" s="21">
         <v>0</v>
       </c>
       <c r="N17" s="18" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="O17" s="3">
         <v>80</v>
@@ -2692,46 +2633,46 @@
     </row>
     <row r="18" spans="1:15" ht="15.75" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G18" s="36" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="H18" s="21">
         <v>1</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="J18" s="21">
         <v>75</v>
       </c>
       <c r="K18" s="36" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="L18" s="36" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="M18" s="21">
         <v>1</v>
       </c>
       <c r="N18" s="18" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="O18" s="3">
         <v>65</v>
@@ -2739,46 +2680,46 @@
     </row>
     <row r="19" spans="1:15" ht="15.75" customHeight="1">
       <c r="A19" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>177</v>
       </c>
       <c r="D19" s="34" t="s">
         <v>54</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G19" s="36" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H19" s="21">
         <v>1</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="J19" s="21">
         <v>80</v>
       </c>
       <c r="K19" s="24" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="L19" s="24" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="M19" s="21">
         <v>1</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="O19" s="3">
         <v>55</v>
@@ -2786,46 +2727,46 @@
     </row>
     <row r="20" spans="1:15" ht="15.75" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D20" s="34" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G20" s="36" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="H20" s="21">
         <v>0</v>
       </c>
       <c r="I20" s="33" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="J20" s="21">
         <v>60</v>
       </c>
       <c r="K20" s="36" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="L20" s="36" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="M20" s="21">
         <v>1</v>
       </c>
       <c r="N20" s="18" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="O20" s="3">
         <v>60</v>
@@ -2918,7 +2859,7 @@
         <v>131</v>
       </c>
       <c r="C36" s="47" t="s">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="D36" s="46" t="s">
         <v>54</v>
@@ -2928,13 +2869,13 @@
         <v>132</v>
       </c>
       <c r="G36" s="47" t="s">
-        <v>137</v>
+        <v>190</v>
       </c>
       <c r="H36" s="47">
         <v>0</v>
       </c>
       <c r="I36" s="47" t="s">
-        <v>138</v>
+        <v>191</v>
       </c>
       <c r="J36" s="46">
         <v>60</v>
@@ -2942,14 +2883,14 @@
       <c r="K36" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="L36" s="46" t="s">
-        <v>134</v>
+      <c r="L36" s="47" t="s">
+        <v>192</v>
       </c>
       <c r="M36" s="46">
         <v>0</v>
       </c>
       <c r="N36" s="47" t="s">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="O36" s="46">
         <v>80</v>

--- a/JsonConverter/ExcelFiles/CBAEvent.xlsx
+++ b/JsonConverter/ExcelFiles/CBAEvent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\CBA\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9568A3E-366F-4D2D-AF09-A0FAB5B1E778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA33499-F70B-48F3-9A9C-D071851CD274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="225">
   <si>
     <t>Event ID</t>
   </si>
@@ -327,9 +327,6 @@
     <t>모래밭 도착</t>
   </si>
   <si>
-    <t>모래밭이 앞을 가로막는다.\n발이 빠질 것 같아…</t>
-  </si>
-  <si>
     <t>돌진한다. 난 쾌남이니까!</t>
   </si>
   <si>
@@ -514,22 +511,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>ㅇㄹㅇㄹㅇㄹㅇㄹ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㅇㄹㅇㄹ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㅇㄹㅇㄹㅇㄹ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㅇㄹㅇㄹㅇㄹㅇㄹㅇㄹ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Prefabs/2D/NPC_CBA/NPC_Frog</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -538,26 +519,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>독독</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅊㄴㅊㄴ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅊㄴㅊ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅊㄴㅊㄴㅊㄴ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅊㄴㅊㄴㅊ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>event_16</t>
   </si>
   <si>
@@ -576,26 +537,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>ㅇㄹㄴㅇ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅇㄹ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅇㄹㄴㅇㄹ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅇㄹㄴ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㄴㄷㄹㅇ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>야구빠따</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -605,22 +546,6 @@
   </si>
   <si>
     <t>Prefabs/2D/NPC_CBA/NPC_BaseballBat</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdse</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㄷㄹㄴㅇㄹ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅇㄹㄷ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴㅇㄹㄷㄴ</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -1163,6 +1088,202 @@
       </rPr>
       <t>!"</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>알록달록한 공룡알이 길 한가운데 나타났다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>건드려볼까..?</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>저쪽으로 굴려보낸다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>안에 뭔가 꿈틀거린다!! 신기해~</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>갑자기 껍질이 깨지기 시작했다!! 너무 놀라서 넘어졌다!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>멀리 굴러갔다. 데구르르… 잘 가….</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>잘 가</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>모래밭이 앞을 가로막는다.\n발이 빠질 것 같아…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>개구리: 독독!\n\n         …… 어떡하지??</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>비켜달라고 부탁해본다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>점프해서 넘어가본다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>독독씨가 비켜주었다. 역시 예의가 있어야 해!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>독독씨가 독침을 쐈다ㅠ 죄송해요 ㅠㅠ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>훌쩍! 멋지게 넘어갔다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>점프하다 독독씨를 짚어버렸다… 앗 따끔해 ㅠ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>모닥불이 타오르고 있다. 따뜻해보인다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>옆에 앉아 쉰다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>따뜻해지고 기운이 난다. 체력+1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>꼬리에 불이 붙었다!!! 헉!!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>산불조심! 불을 끈다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>불이 잘 꺼졌다. 안전제일!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>털에 불이 붙었다!! 꺄악!!ㅠㅠ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>휘둘러본다</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>들고 간다. 무기 획득!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>완벽한 스윙! 안타홈런!! (1점추가)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>빠따를 놓쳐 날아갔다. 어딘가에서 비명소리가 들린다..</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">든든하다. 이제 뭐든 두렵지 않다곰! </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>헉 너무 무겁다… 체력이 오히려 빠졌다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>사망원인</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeathResult</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌뿌리에 걸려 넘어졌다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>혈당 스파이크로 잠에 빠졌다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무에게 쫓겨났다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>독버섯을 먹고 쓰러졌다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무에서 떨어져 다쳤다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>돼지머리에게 당했다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>허리를 삐끗해 쓰러졌다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>독이 오른 감자를 먹었다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>모래밭에 빠졌다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>개한테 쫓겼다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>책의 저주에 걸렸다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>수상한 남자한테 당했다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>여우가 물었다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>공룡알에 당했다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>독독씨한테 쏘였다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>불이 붙었다….</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>야구빠따를 집는 게 아니었다… 이놈의 야구…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>모자따위 무시했어야 했다…</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1313,7 +1434,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1371,6 +1492,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8D5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1455,7 +1582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1570,6 +1697,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1807,20 +1940,20 @@
   <cols>
     <col min="1" max="1" width="9.7109375" style="3" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="33.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="40.7109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="26.140625" style="3" customWidth="1"/>
     <col min="5" max="5" width="31.42578125" style="22" customWidth="1"/>
     <col min="6" max="6" width="21.42578125" style="22" customWidth="1"/>
     <col min="7" max="7" width="54.42578125" style="22" customWidth="1"/>
     <col min="8" max="8" width="19.140625" style="22" customWidth="1"/>
     <col min="9" max="9" width="43.28515625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" style="22" customWidth="1"/>
     <col min="11" max="11" width="21.7109375" style="22" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="45.7109375" style="22" customWidth="1"/>
     <col min="13" max="13" width="33.140625" style="22" customWidth="1"/>
     <col min="14" max="14" width="37.140625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="19.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="11.140625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="36.28515625" style="3" customWidth="1"/>
     <col min="17" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
@@ -1840,20 +1973,23 @@
       <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="55" t="s">
+      <c r="F1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="52" t="s">
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="54"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="2" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="2" spans="1:17" ht="12.75" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -1878,7 +2014,7 @@
         <v>7</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>7</v>
@@ -1893,13 +2029,16 @@
         <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>8</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="12" customFormat="1" ht="15.75" customHeight="1">
@@ -1925,12 +2064,12 @@
         <v>13</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="J3" s="53" t="s">
         <v>15</v>
       </c>
       <c r="K3" s="26" t="s">
@@ -1940,13 +2079,16 @@
         <v>17</v>
       </c>
       <c r="M3" s="20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="O3" s="20" t="s">
+      <c r="O3" s="53" t="s">
         <v>19</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="15.75" customHeight="1">
@@ -1995,7 +2137,9 @@
       <c r="O4" s="5">
         <v>70</v>
       </c>
-      <c r="P4" s="5"/>
+      <c r="P4" s="23" t="s">
+        <v>207</v>
+      </c>
       <c r="Q4" s="5"/>
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
@@ -2044,7 +2188,9 @@
       <c r="O5" s="5">
         <v>45</v>
       </c>
-      <c r="P5" s="5"/>
+      <c r="P5" s="23" t="s">
+        <v>208</v>
+      </c>
       <c r="Q5" s="5"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
@@ -2093,7 +2239,9 @@
       <c r="O6" s="5">
         <v>70</v>
       </c>
-      <c r="P6" s="5"/>
+      <c r="P6" s="23" t="s">
+        <v>209</v>
+      </c>
       <c r="Q6" s="5"/>
     </row>
     <row r="7" spans="1:17" ht="15.75" customHeight="1">
@@ -2116,7 +2264,7 @@
         <v>56</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H7" s="19">
         <v>1</v>
@@ -2142,7 +2290,9 @@
       <c r="O7" s="5">
         <v>55</v>
       </c>
-      <c r="P7" s="5"/>
+      <c r="P7" s="23" t="s">
+        <v>210</v>
+      </c>
       <c r="Q7" s="5"/>
     </row>
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
@@ -2191,7 +2341,9 @@
       <c r="O8" s="5">
         <v>75</v>
       </c>
-      <c r="P8" s="5"/>
+      <c r="P8" s="23" t="s">
+        <v>211</v>
+      </c>
       <c r="Q8" s="5"/>
     </row>
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
@@ -2214,7 +2366,7 @@
         <v>75</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H9" s="19">
         <v>0</v>
@@ -2240,7 +2392,9 @@
       <c r="O9" s="5">
         <v>60</v>
       </c>
-      <c r="P9" s="5"/>
+      <c r="P9" s="23" t="s">
+        <v>212</v>
+      </c>
       <c r="Q9" s="5"/>
     </row>
     <row r="10" spans="1:17" ht="15.75" customHeight="1">
@@ -2257,7 +2411,7 @@
         <v>23</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="F10" s="24" t="s">
         <v>83</v>
@@ -2289,7 +2443,9 @@
       <c r="O10" s="5">
         <v>100</v>
       </c>
-      <c r="P10" s="5"/>
+      <c r="P10" s="23" t="s">
+        <v>213</v>
+      </c>
       <c r="Q10" s="5"/>
     </row>
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
@@ -2306,7 +2462,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="F11" s="36" t="s">
         <v>92</v>
@@ -2338,7 +2494,9 @@
       <c r="O11" s="5">
         <v>70</v>
       </c>
-      <c r="P11" s="5"/>
+      <c r="P11" s="23" t="s">
+        <v>214</v>
+      </c>
       <c r="Q11" s="5"/>
     </row>
     <row r="12" spans="1:17" ht="15.75" customHeight="1">
@@ -2349,132 +2507,136 @@
         <v>99</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="F12" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G12" s="19" t="s">
         <v>101</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>102</v>
       </c>
       <c r="H12" s="19">
         <v>0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J12" s="19">
         <v>45</v>
       </c>
       <c r="K12" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12" s="19" t="s">
         <v>104</v>
-      </c>
-      <c r="L12" s="19" t="s">
-        <v>105</v>
       </c>
       <c r="M12" s="19">
         <v>0</v>
       </c>
       <c r="N12" s="23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O12" s="5">
         <v>70</v>
       </c>
-      <c r="P12" s="5"/>
+      <c r="P12" s="23" t="s">
+        <v>215</v>
+      </c>
       <c r="Q12" s="5"/>
     </row>
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="C13" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="D13" s="34" t="s">
         <v>54</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H13" s="1">
         <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J13" s="1">
         <v>65</v>
       </c>
       <c r="K13" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="M13" s="1">
         <v>0</v>
       </c>
       <c r="N13" s="42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O13" s="5">
         <v>55</v>
       </c>
-      <c r="P13" s="5"/>
+      <c r="P13" s="23" t="s">
+        <v>216</v>
+      </c>
       <c r="Q13" s="5"/>
     </row>
     <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="C14" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="F14" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="D14" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="F14" s="43" t="s">
+      <c r="G14" s="44" t="s">
         <v>118</v>
-      </c>
-      <c r="G14" s="44" t="s">
-        <v>119</v>
       </c>
       <c r="H14" s="44">
         <v>0</v>
       </c>
       <c r="I14" s="29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J14" s="30">
         <v>55</v>
       </c>
       <c r="K14" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="L14" s="43" t="s">
         <v>121</v>
-      </c>
-      <c r="L14" s="43" t="s">
-        <v>122</v>
       </c>
       <c r="M14" s="43">
         <v>0</v>
@@ -2485,429 +2647,451 @@
       <c r="O14" s="5">
         <v>100</v>
       </c>
-      <c r="P14" s="5"/>
+      <c r="P14" s="42" t="s">
+        <v>217</v>
+      </c>
       <c r="Q14" s="5"/>
     </row>
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="B15" s="33" t="s">
-        <v>124</v>
-      </c>
       <c r="C15" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D15" s="34" t="s">
         <v>54</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H15" s="48">
         <v>1</v>
       </c>
       <c r="I15" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J15" s="21">
         <v>40</v>
       </c>
       <c r="K15" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="L15" s="36" t="s">
         <v>127</v>
-      </c>
-      <c r="L15" s="36" t="s">
-        <v>128</v>
       </c>
       <c r="M15" s="36">
         <v>0</v>
       </c>
       <c r="N15" s="33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O15" s="5">
         <v>70</v>
       </c>
-      <c r="P15" s="5"/>
+      <c r="P15" s="33" t="s">
+        <v>218</v>
+      </c>
       <c r="Q15" s="5"/>
     </row>
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" s="51" t="s">
         <v>145</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>146</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E16" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="F16" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="F16" s="24" t="s">
-        <v>148</v>
-      </c>
       <c r="G16" s="24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H16" s="21">
         <v>0</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J16" s="21">
         <v>30</v>
       </c>
       <c r="K16" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="L16" s="24" t="s">
         <v>151</v>
-      </c>
-      <c r="L16" s="24" t="s">
-        <v>152</v>
       </c>
       <c r="M16" s="21">
         <v>0</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O16" s="3">
         <v>70</v>
       </c>
+      <c r="P16" s="18" t="s">
+        <v>219</v>
+      </c>
     </row>
-    <row r="17" spans="1:15" ht="15.75" customHeight="1">
+    <row r="17" spans="1:16" ht="15.75" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="H17" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="J17" s="21">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="K17" s="36" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="L17" s="36" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="M17" s="21">
         <v>0</v>
       </c>
       <c r="N17" s="18" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="O17" s="3">
-        <v>80</v>
+        <v>100</v>
+      </c>
+      <c r="P17" s="18" t="s">
+        <v>220</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15.75" customHeight="1">
+    <row r="18" spans="1:16" ht="15.75" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="G18" s="36" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="H18" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="J18" s="21">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="K18" s="36" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="L18" s="36" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="M18" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="18" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="O18" s="3">
-        <v>65</v>
+        <v>55</v>
+      </c>
+      <c r="P18" s="18" t="s">
+        <v>221</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15.75" customHeight="1">
+    <row r="19" spans="1:16" ht="15.75" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="D19" s="34" t="s">
         <v>54</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="G19" s="36" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="H19" s="21">
         <v>1</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="J19" s="21">
         <v>80</v>
       </c>
       <c r="K19" s="24" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="L19" s="24" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="M19" s="21">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="O19" s="3">
+        <v>70</v>
+      </c>
+      <c r="P19" s="18" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A20" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="F20" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="G20" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="H20" s="21">
         <v>1</v>
       </c>
-      <c r="N19" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="O19" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A20" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="D20" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="G20" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="H20" s="21">
-        <v>0</v>
-      </c>
       <c r="I20" s="33" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="J20" s="21">
         <v>60</v>
       </c>
-      <c r="K20" s="36" t="s">
-        <v>182</v>
+      <c r="K20" s="52" t="s">
+        <v>199</v>
       </c>
       <c r="L20" s="36" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="M20" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" s="18" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="O20" s="3">
-        <v>60</v>
+        <v>55</v>
+      </c>
+      <c r="P20" s="18" t="s">
+        <v>223</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15.75" customHeight="1">
+    <row r="21" spans="1:16" ht="15.75" customHeight="1">
       <c r="A21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
     </row>
-    <row r="22" spans="1:15" ht="15.75" customHeight="1">
+    <row r="22" spans="1:16" ht="15.75" customHeight="1">
       <c r="A22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
     </row>
-    <row r="23" spans="1:15" ht="15.75" customHeight="1">
+    <row r="23" spans="1:16" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
     </row>
-    <row r="24" spans="1:15" ht="15.75" customHeight="1">
+    <row r="24" spans="1:16" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
     </row>
-    <row r="25" spans="1:15" ht="15.75" customHeight="1">
+    <row r="25" spans="1:16" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="F25" s="21"/>
     </row>
-    <row r="26" spans="1:15" ht="15.75" customHeight="1">
+    <row r="26" spans="1:16" ht="15.75" customHeight="1">
       <c r="A26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="F26" s="21"/>
     </row>
-    <row r="27" spans="1:15" ht="15.75" customHeight="1">
+    <row r="27" spans="1:16" ht="15.75" customHeight="1">
       <c r="A27" s="9"/>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="F27" s="21"/>
     </row>
-    <row r="28" spans="1:15" ht="15.75" customHeight="1">
+    <row r="28" spans="1:16" ht="15.75" customHeight="1">
       <c r="A28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="F28" s="21"/>
     </row>
-    <row r="29" spans="1:15" ht="15.75" customHeight="1">
+    <row r="29" spans="1:16" ht="15.75" customHeight="1">
       <c r="A29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
     </row>
-    <row r="30" spans="1:15" ht="15.75" customHeight="1">
+    <row r="30" spans="1:16" ht="15.75" customHeight="1">
       <c r="A30" s="9"/>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
     </row>
-    <row r="31" spans="1:15" ht="15.75" customHeight="1">
+    <row r="31" spans="1:16" ht="15.75" customHeight="1">
       <c r="A31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
     </row>
-    <row r="32" spans="1:15" ht="15.75" customHeight="1">
+    <row r="32" spans="1:16" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
     </row>
-    <row r="33" spans="1:15" ht="15.75" customHeight="1">
+    <row r="33" spans="1:16" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
     </row>
-    <row r="34" spans="1:15" ht="15.75" customHeight="1">
+    <row r="34" spans="1:16" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
     </row>
-    <row r="35" spans="1:15" ht="15.75" customHeight="1">
+    <row r="35" spans="1:16" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
     </row>
-    <row r="36" spans="1:15" ht="54.95" customHeight="1">
+    <row r="36" spans="1:16" ht="54.95" customHeight="1">
       <c r="A36" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="45" t="s">
         <v>130</v>
       </c>
-      <c r="B36" s="45" t="s">
-        <v>131</v>
-      </c>
       <c r="C36" s="47" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="D36" s="46" t="s">
         <v>54</v>
       </c>
       <c r="E36" s="46"/>
       <c r="F36" s="46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G36" s="47" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="H36" s="47">
         <v>0</v>
       </c>
       <c r="I36" s="47" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="J36" s="46">
         <v>60</v>
       </c>
       <c r="K36" s="46" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L36" s="47" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="M36" s="46">
         <v>0</v>
       </c>
       <c r="N36" s="47" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="O36" s="46">
         <v>80</v>
       </c>
+      <c r="P36" s="18" t="s">
+        <v>224</v>
+      </c>
     </row>
-    <row r="37" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:16" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:16" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:16" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:16" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:16" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:16" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:16" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:16" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:16" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:16" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:16" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:16" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -3867,6 +4051,6 @@
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/CBAEvent.xlsx
+++ b/JsonConverter/ExcelFiles/CBAEvent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\CBA\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA33499-F70B-48F3-9A9C-D071851CD274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9A983A-F685-407D-A4CB-B0D34BDB2BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1215,75 +1215,75 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>돌뿌리에 걸려 넘어졌다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>혈당 스파이크로 잠에 빠졌다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무에게 쫓겨났다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>독버섯을 먹고 쓰러졌다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무에서 떨어져 다쳤다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>돼지머리에게 당했다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>허리를 삐끗해 쓰러졌다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>독이 오른 감자를 먹었다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>모래밭에 빠졌다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>개한테 쫓겼다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>책의 저주에 걸렸다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>수상한 남자한테 당했다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>여우가 물었다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>공룡알에 당했다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>독독씨한테 쏘였다…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>불이 붙었다….</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>야구빠따를 집는 게 아니었다… 이놈의 야구…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>모자따위 무시했어야 했다…</t>
+    <t xml:space="preserve"> 돌뿌리에 걸려 넘어졌다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 혈당 스파이크로 잠에 빠졌다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 나무에게 쫓겨났다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 독버섯을 먹고 쓰러졌다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 나무에서 떨어져 다쳤다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 돼지머리에게 당했다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 허리를 삐끗해 쓰러졌다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 독이 오른 감자를 먹었다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 모래밭에 빠졌다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 개한테 쫓겼다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 책의 저주에 걸렸다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 수상한 남자한테 당했다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 여우가 물었다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 공룡알에 당했다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 독독씨한테 쏘였다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 불이 붙었다….</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 야구빠따를 집는 게 아니었다… 이놈의 야구…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 모자따위 무시했어야 했다…</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
